--- a/research/traditional_assets/database/data/greece/greece_heathcare_information_and_technology.xlsx
+++ b/research/traditional_assets/database/data/greece/greece_heathcare_information_and_technology.xlsx
@@ -1266,7 +1266,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1403,22 +1403,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.135880873987394</v>
+        <v>0.1356170360646217</v>
       </c>
       <c r="C2">
-        <v>2.528670981618014</v>
+        <v>2.509736774264544</v>
       </c>
       <c r="D2">
-        <v>2.163670981618013</v>
+        <v>2.170026774264544</v>
       </c>
       <c r="E2">
-        <v>-0.029</v>
+        <v>-0.003710000000000001</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.02529</v>
       </c>
       <c r="G2">
         <v>0.365</v>
@@ -1439,28 +1439,28 @@
         <v>0.236</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.001272087</v>
       </c>
       <c r="N2">
-        <v>0.236</v>
+        <v>0.234727913</v>
       </c>
       <c r="O2">
-        <v>0.05192</v>
+        <v>0.05164014086</v>
       </c>
       <c r="P2">
-        <v>0.18408</v>
+        <v>0.18308777214</v>
       </c>
       <c r="Q2">
-        <v>0.18608</v>
+        <v>0.18508777214</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.135880873987394</v>
+        <v>0.1365906020854765</v>
       </c>
       <c r="T2">
-        <v>1.174055766301309</v>
+        <v>1.183305902641865</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1477,7 +1477,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>185.5219021969409</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1485,22 +1485,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1356170360646217</v>
+        <v>0.1353531981418495</v>
       </c>
       <c r="C3">
-        <v>2.509736774264544</v>
+        <v>2.490840017257109</v>
       </c>
       <c r="D3">
-        <v>2.170026774264544</v>
+        <v>2.176420017257109</v>
       </c>
       <c r="E3">
-        <v>-0.003710000000000001</v>
+        <v>0.02158</v>
       </c>
       <c r="F3">
-        <v>0.02529</v>
+        <v>0.05058</v>
       </c>
       <c r="G3">
         <v>0.365</v>
@@ -1521,28 +1521,28 @@
         <v>0.236</v>
       </c>
       <c r="M3">
-        <v>0.001272087</v>
+        <v>0.002544174</v>
       </c>
       <c r="N3">
-        <v>0.234727913</v>
+        <v>0.233455826</v>
       </c>
       <c r="O3">
-        <v>0.05164014086</v>
+        <v>0.05136028172</v>
       </c>
       <c r="P3">
-        <v>0.18308777214</v>
+        <v>0.18209554428</v>
       </c>
       <c r="Q3">
-        <v>0.18508777214</v>
+        <v>0.18409554428</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1365906020854765</v>
+        <v>0.1373148144304586</v>
       </c>
       <c r="T3">
-        <v>1.183305902641865</v>
+        <v>1.192744817275085</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1559,7 +1559,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>185.5219021969409</v>
+        <v>92.76095109847047</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1567,22 +1567,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1353531981418495</v>
+        <v>0.1350893602190772</v>
       </c>
       <c r="C4">
-        <v>2.490840017257109</v>
+        <v>2.471981042577754</v>
       </c>
       <c r="D4">
-        <v>2.176420017257109</v>
+        <v>2.182851042577755</v>
       </c>
       <c r="E4">
-        <v>0.02158</v>
+        <v>0.04686999999999999</v>
       </c>
       <c r="F4">
-        <v>0.05058</v>
+        <v>0.07586999999999999</v>
       </c>
       <c r="G4">
         <v>0.365</v>
@@ -1603,28 +1603,28 @@
         <v>0.236</v>
       </c>
       <c r="M4">
-        <v>0.002544174</v>
+        <v>0.003816261</v>
       </c>
       <c r="N4">
-        <v>0.233455826</v>
+        <v>0.232183739</v>
       </c>
       <c r="O4">
-        <v>0.05136028172</v>
+        <v>0.05108042258</v>
       </c>
       <c r="P4">
-        <v>0.18209554428</v>
+        <v>0.18110331642</v>
       </c>
       <c r="Q4">
-        <v>0.18409554428</v>
+        <v>0.18310331642</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1373148144304586</v>
+        <v>0.1380539589887394</v>
       </c>
       <c r="T4">
-        <v>1.192744817275085</v>
+        <v>1.202378348704866</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>92.76095109847047</v>
+        <v>61.84063406564698</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1649,22 +1649,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1350893602190772</v>
+        <v>0.1348255222963049</v>
       </c>
       <c r="C5">
-        <v>2.471981042577754</v>
+        <v>2.453160186144002</v>
       </c>
       <c r="D5">
-        <v>2.182851042577755</v>
+        <v>2.189320186144002</v>
       </c>
       <c r="E5">
-        <v>0.04686999999999999</v>
+        <v>0.07216</v>
       </c>
       <c r="F5">
-        <v>0.07586999999999999</v>
+        <v>0.10116</v>
       </c>
       <c r="G5">
         <v>0.365</v>
@@ -1685,28 +1685,28 @@
         <v>0.236</v>
       </c>
       <c r="M5">
-        <v>0.003816261</v>
+        <v>0.005088347999999999</v>
       </c>
       <c r="N5">
-        <v>0.232183739</v>
+        <v>0.230911652</v>
       </c>
       <c r="O5">
-        <v>0.05108042258</v>
+        <v>0.05080056344</v>
       </c>
       <c r="P5">
-        <v>0.18110331642</v>
+        <v>0.18011108856</v>
       </c>
       <c r="Q5">
-        <v>0.18310331642</v>
+        <v>0.18211108856</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1380539589887394</v>
+        <v>0.1388085023919843</v>
       </c>
       <c r="T5">
-        <v>1.202378348704866</v>
+        <v>1.212212578706102</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1723,7 +1723,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>61.84063406564698</v>
+        <v>46.38047554923524</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1731,22 +1731,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1348255222963049</v>
+        <v>0.1345616843735327</v>
       </c>
       <c r="C6">
-        <v>2.453160186144002</v>
+        <v>2.43437778786734</v>
       </c>
       <c r="D6">
-        <v>2.189320186144002</v>
+        <v>2.19582778786734</v>
       </c>
       <c r="E6">
-        <v>0.07216</v>
+        <v>0.09745000000000001</v>
       </c>
       <c r="F6">
-        <v>0.10116</v>
+        <v>0.12645</v>
       </c>
       <c r="G6">
         <v>0.365</v>
@@ -1767,28 +1767,28 @@
         <v>0.236</v>
       </c>
       <c r="M6">
-        <v>0.005088347999999999</v>
+        <v>0.006360435</v>
       </c>
       <c r="N6">
-        <v>0.230911652</v>
+        <v>0.229639565</v>
       </c>
       <c r="O6">
-        <v>0.05080056344</v>
+        <v>0.0505207043</v>
       </c>
       <c r="P6">
-        <v>0.18011108856</v>
+        <v>0.1791188607</v>
       </c>
       <c r="Q6">
-        <v>0.18211108856</v>
+        <v>0.1811188607</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1388085023919843</v>
+        <v>0.1395789309195081</v>
       </c>
       <c r="T6">
-        <v>1.212212578706102</v>
+        <v>1.222253845128416</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1805,7 +1805,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>46.38047554923524</v>
+        <v>37.10438043938819</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1813,22 +1813,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1345616843735327</v>
+        <v>0.1342978464507604</v>
       </c>
       <c r="C7">
-        <v>2.43437778786734</v>
+        <v>2.415634191712759</v>
       </c>
       <c r="D7">
-        <v>2.19582778786734</v>
+        <v>2.20237419171276</v>
       </c>
       <c r="E7">
-        <v>0.09745000000000001</v>
+        <v>0.12274</v>
       </c>
       <c r="F7">
-        <v>0.12645</v>
+        <v>0.15174</v>
       </c>
       <c r="G7">
         <v>0.365</v>
@@ -1849,28 +1849,28 @@
         <v>0.236</v>
       </c>
       <c r="M7">
-        <v>0.006360435</v>
+        <v>0.007632522</v>
       </c>
       <c r="N7">
-        <v>0.229639565</v>
+        <v>0.228367478</v>
       </c>
       <c r="O7">
-        <v>0.0505207043</v>
+        <v>0.05024084516</v>
       </c>
       <c r="P7">
-        <v>0.1791188607</v>
+        <v>0.17812663284</v>
       </c>
       <c r="Q7">
-        <v>0.1811188607</v>
+        <v>0.18012663284</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1395789309195081</v>
+        <v>0.1403657515433621</v>
       </c>
       <c r="T7">
-        <v>1.222253845128416</v>
+        <v>1.232508755517161</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1887,7 +1887,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>37.10438043938819</v>
+        <v>30.92031703282349</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1895,22 +1895,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1342978464507604</v>
+        <v>0.1340340085279881</v>
       </c>
       <c r="C8">
-        <v>2.415634191712759</v>
+        <v>2.396929745759353</v>
       </c>
       <c r="D8">
-        <v>2.20237419171276</v>
+        <v>2.208959745759353</v>
       </c>
       <c r="E8">
-        <v>0.12274</v>
+        <v>0.14803</v>
       </c>
       <c r="F8">
-        <v>0.15174</v>
+        <v>0.17703</v>
       </c>
       <c r="G8">
         <v>0.365</v>
@@ -1931,28 +1931,28 @@
         <v>0.236</v>
       </c>
       <c r="M8">
-        <v>0.007632521999999999</v>
+        <v>0.008904608999999997</v>
       </c>
       <c r="N8">
-        <v>0.228367478</v>
+        <v>0.227095391</v>
       </c>
       <c r="O8">
-        <v>0.05024084516</v>
+        <v>0.04996098601999999</v>
       </c>
       <c r="P8">
-        <v>0.17812663284</v>
+        <v>0.17713440498</v>
       </c>
       <c r="Q8">
-        <v>0.18012663284</v>
+        <v>0.17913440498</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1403657515433621</v>
+        <v>0.1411694930408474</v>
       </c>
       <c r="T8">
-        <v>1.232508755517161</v>
+        <v>1.242984201613192</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1969,7 +1969,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>30.92031703282349</v>
+        <v>26.50312888527728</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1340340085279881</v>
+        <v>0.1337701706052159</v>
       </c>
       <c r="C9">
-        <v>2.396929745759353</v>
+        <v>2.37826480226202</v>
       </c>
       <c r="D9">
-        <v>2.208959745759353</v>
+        <v>2.215584802262019</v>
       </c>
       <c r="E9">
-        <v>0.14803</v>
+        <v>0.17332</v>
       </c>
       <c r="F9">
-        <v>0.17703</v>
+        <v>0.20232</v>
       </c>
       <c r="G9">
         <v>0.365</v>
@@ -2013,28 +2013,28 @@
         <v>0.236</v>
       </c>
       <c r="M9">
-        <v>0.008904609000000001</v>
+        <v>0.010176696</v>
       </c>
       <c r="N9">
-        <v>0.227095391</v>
+        <v>0.225823304</v>
       </c>
       <c r="O9">
-        <v>0.04996098601999999</v>
+        <v>0.04968112688</v>
       </c>
       <c r="P9">
-        <v>0.17713440498</v>
+        <v>0.17614217712</v>
       </c>
       <c r="Q9">
-        <v>0.17913440498</v>
+        <v>0.17814217712</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1411694930408475</v>
+        <v>0.1419907071795825</v>
       </c>
       <c r="T9">
-        <v>1.242984201613193</v>
+        <v>1.253687374798268</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2051,7 +2051,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>26.50312888527727</v>
+        <v>23.19023777461762</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2059,22 +2059,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1337701706052159</v>
+        <v>0.1335063326824436</v>
       </c>
       <c r="C10">
-        <v>2.37826480226202</v>
+        <v>2.359639717714261</v>
       </c>
       <c r="D10">
-        <v>2.215584802262019</v>
+        <v>2.222249717714261</v>
       </c>
       <c r="E10">
-        <v>0.17332</v>
+        <v>0.19861</v>
       </c>
       <c r="F10">
-        <v>0.20232</v>
+        <v>0.22761</v>
       </c>
       <c r="G10">
         <v>0.365</v>
@@ -2095,28 +2095,28 @@
         <v>0.236</v>
       </c>
       <c r="M10">
-        <v>0.010176696</v>
+        <v>0.011448783</v>
       </c>
       <c r="N10">
-        <v>0.225823304</v>
+        <v>0.224551217</v>
       </c>
       <c r="O10">
-        <v>0.04968112688</v>
+        <v>0.04940126774</v>
       </c>
       <c r="P10">
-        <v>0.17614217712</v>
+        <v>0.17514994926</v>
       </c>
       <c r="Q10">
-        <v>0.17814217712</v>
+        <v>0.17714994926</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1419907071795825</v>
+        <v>0.1428299699807072</v>
       </c>
       <c r="T10">
-        <v>1.253687374798268</v>
+        <v>1.264625782558839</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2133,7 +2133,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>23.19023777461762</v>
+        <v>20.61354468854899</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2141,22 +2141,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1335063326824436</v>
+        <v>0.1332424947596713</v>
       </c>
       <c r="C11">
-        <v>2.359639717714261</v>
+        <v>2.341054852912134</v>
       </c>
       <c r="D11">
-        <v>2.222249717714261</v>
+        <v>2.228954852912134</v>
       </c>
       <c r="E11">
-        <v>0.19861</v>
+        <v>0.2239</v>
       </c>
       <c r="F11">
-        <v>0.22761</v>
+        <v>0.2529</v>
       </c>
       <c r="G11">
         <v>0.365</v>
@@ -2177,28 +2177,28 @@
         <v>0.236</v>
       </c>
       <c r="M11">
-        <v>0.011448783</v>
+        <v>0.01272087</v>
       </c>
       <c r="N11">
-        <v>0.224551217</v>
+        <v>0.22327913</v>
       </c>
       <c r="O11">
-        <v>0.04940126774</v>
+        <v>0.0491214086</v>
       </c>
       <c r="P11">
-        <v>0.17514994926</v>
+        <v>0.1741577214</v>
       </c>
       <c r="Q11">
-        <v>0.17714994926</v>
+        <v>0.1761577214</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1428299699807072</v>
+        <v>0.1436878830663015</v>
       </c>
       <c r="T11">
-        <v>1.264625782558839</v>
+        <v>1.275807266047423</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2215,7 +2215,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>20.61354468854899</v>
+        <v>18.5521902196941</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2223,22 +2223,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1332424947596713</v>
+        <v>0.1329786568368991</v>
       </c>
       <c r="C12">
-        <v>2.341054852912134</v>
+        <v>2.322510573019359</v>
       </c>
       <c r="D12">
-        <v>2.228954852912134</v>
+        <v>2.235700573019359</v>
       </c>
       <c r="E12">
-        <v>0.2239</v>
+        <v>0.24919</v>
       </c>
       <c r="F12">
-        <v>0.2529</v>
+        <v>0.27819</v>
       </c>
       <c r="G12">
         <v>0.365</v>
@@ -2259,28 +2259,28 @@
         <v>0.236</v>
       </c>
       <c r="M12">
-        <v>0.01272087</v>
+        <v>0.013992957</v>
       </c>
       <c r="N12">
-        <v>0.22327913</v>
+        <v>0.222007043</v>
       </c>
       <c r="O12">
-        <v>0.0491214086</v>
+        <v>0.04884154945999999</v>
       </c>
       <c r="P12">
-        <v>0.1741577214</v>
+        <v>0.17316549354</v>
       </c>
       <c r="Q12">
-        <v>0.1761577214</v>
+        <v>0.17516549354</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1436878830663015</v>
+        <v>0.1445650750976394</v>
       </c>
       <c r="T12">
-        <v>1.275807266047423</v>
+        <v>1.287240018827885</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2297,7 +2297,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>18.55219021969409</v>
+        <v>16.86562747244918</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2305,22 +2305,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1329786568368991</v>
+        <v>0.1327148189141268</v>
       </c>
       <c r="C13">
-        <v>2.322510573019359</v>
+        <v>2.304007247633604</v>
       </c>
       <c r="D13">
-        <v>2.235700573019359</v>
+        <v>2.242487247633604</v>
       </c>
       <c r="E13">
-        <v>0.24919</v>
+        <v>0.2744799999999999</v>
       </c>
       <c r="F13">
-        <v>0.27819</v>
+        <v>0.30348</v>
       </c>
       <c r="G13">
         <v>0.365</v>
@@ -2341,28 +2341,28 @@
         <v>0.236</v>
       </c>
       <c r="M13">
-        <v>0.013992957</v>
+        <v>0.015265044</v>
       </c>
       <c r="N13">
-        <v>0.222007043</v>
+        <v>0.220734956</v>
       </c>
       <c r="O13">
-        <v>0.04884154945999999</v>
+        <v>0.04856169032</v>
       </c>
       <c r="P13">
-        <v>0.17316549354</v>
+        <v>0.17217326568</v>
       </c>
       <c r="Q13">
-        <v>0.17516549354</v>
+        <v>0.17417326568</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1445650750976394</v>
+        <v>0.1454622033115077</v>
       </c>
       <c r="T13">
-        <v>1.287240018827885</v>
+        <v>1.298932606898812</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2379,7 +2379,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>16.86562747244918</v>
+        <v>15.46015851641175</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2387,22 +2387,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1327148189141268</v>
+        <v>0.1324509809913545</v>
       </c>
       <c r="C14">
-        <v>2.304007247633604</v>
+        <v>2.285545250853994</v>
       </c>
       <c r="D14">
-        <v>2.242487247633604</v>
+        <v>2.249315250853994</v>
       </c>
       <c r="E14">
-        <v>0.2744799999999999</v>
+        <v>0.29977</v>
       </c>
       <c r="F14">
-        <v>0.30348</v>
+        <v>0.32877</v>
       </c>
       <c r="G14">
         <v>0.365</v>
@@ -2423,28 +2423,28 @@
         <v>0.236</v>
       </c>
       <c r="M14">
-        <v>0.015265044</v>
+        <v>0.016537131</v>
       </c>
       <c r="N14">
-        <v>0.220734956</v>
+        <v>0.219462869</v>
       </c>
       <c r="O14">
-        <v>0.04856169032</v>
+        <v>0.04828183118</v>
       </c>
       <c r="P14">
-        <v>0.17217326568</v>
+        <v>0.17118103782</v>
       </c>
       <c r="Q14">
-        <v>0.17417326568</v>
+        <v>0.17318103782</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1454622033115077</v>
+        <v>0.1463799551624765</v>
       </c>
       <c r="T14">
-        <v>1.298932606898812</v>
+        <v>1.310893990097806</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2461,7 +2461,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>15.46015851641175</v>
+        <v>14.27091555361084</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2469,22 +2469,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1324509809913545</v>
+        <v>0.1321871430685823</v>
       </c>
       <c r="C15">
-        <v>2.285545250853994</v>
+        <v>2.267124961349851</v>
       </c>
       <c r="D15">
-        <v>2.249315250853994</v>
+        <v>2.256184961349851</v>
       </c>
       <c r="E15">
-        <v>0.29977</v>
+        <v>0.32506</v>
       </c>
       <c r="F15">
-        <v>0.32877</v>
+        <v>0.35406</v>
       </c>
       <c r="G15">
         <v>0.365</v>
@@ -2505,28 +2505,28 @@
         <v>0.236</v>
       </c>
       <c r="M15">
-        <v>0.016537131</v>
+        <v>0.017809218</v>
       </c>
       <c r="N15">
-        <v>0.219462869</v>
+        <v>0.218190782</v>
       </c>
       <c r="O15">
-        <v>0.04828183118</v>
+        <v>0.04800197203999999</v>
       </c>
       <c r="P15">
-        <v>0.17118103782</v>
+        <v>0.17018880996</v>
       </c>
       <c r="Q15">
-        <v>0.17318103782</v>
+        <v>0.17218880996</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1463799551624765</v>
+        <v>0.1473190500797468</v>
       </c>
       <c r="T15">
-        <v>1.310893990097806</v>
+        <v>1.323133544999103</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2543,7 +2543,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>14.27091555361084</v>
+        <v>13.25156444263864</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2551,22 +2551,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1321871430685823</v>
+        <v>0.13209880514581</v>
       </c>
       <c r="C16">
-        <v>2.267124961349851</v>
+        <v>2.244144456742503</v>
       </c>
       <c r="D16">
-        <v>2.256184961349851</v>
+        <v>2.258494456742504</v>
       </c>
       <c r="E16">
-        <v>0.32506</v>
+        <v>0.35035</v>
       </c>
       <c r="F16">
-        <v>0.35406</v>
+        <v>0.37935</v>
       </c>
       <c r="G16">
         <v>0.365</v>
@@ -2587,45 +2587,45 @@
         <v>0.236</v>
       </c>
       <c r="M16">
-        <v>0.017809218</v>
+        <v>0.01965033</v>
       </c>
       <c r="N16">
-        <v>0.218190782</v>
+        <v>0.21634967</v>
       </c>
       <c r="O16">
-        <v>0.04800197203999999</v>
+        <v>0.0475969274</v>
       </c>
       <c r="P16">
-        <v>0.17018880996</v>
+        <v>0.1687527426</v>
       </c>
       <c r="Q16">
-        <v>0.17218880996</v>
+        <v>0.1707527426</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1473190500797468</v>
+        <v>0.1482802413480118</v>
       </c>
       <c r="T16">
-        <v>1.323133544999103</v>
+        <v>1.335661089427489</v>
       </c>
       <c r="U16">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V16">
         <v>0.22</v>
       </c>
       <c r="W16">
-        <v>0.039234</v>
+        <v>0.040404</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y16">
-        <v>13.25156444263864</v>
+        <v>12.00997642278781</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2633,22 +2633,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.13209880514581</v>
+        <v>0.1318466672230377</v>
       </c>
       <c r="C17">
-        <v>2.244144456742503</v>
+        <v>2.225472401623967</v>
       </c>
       <c r="D17">
-        <v>2.258494456742504</v>
+        <v>2.265112401623967</v>
       </c>
       <c r="E17">
-        <v>0.3503499999999999</v>
+        <v>0.37564</v>
       </c>
       <c r="F17">
-        <v>0.37935</v>
+        <v>0.40464</v>
       </c>
       <c r="G17">
         <v>0.365</v>
@@ -2669,28 +2669,28 @@
         <v>0.236</v>
       </c>
       <c r="M17">
-        <v>0.01965033</v>
+        <v>0.020960352</v>
       </c>
       <c r="N17">
-        <v>0.21634967</v>
+        <v>0.215039648</v>
       </c>
       <c r="O17">
-        <v>0.0475969274</v>
+        <v>0.04730872256</v>
       </c>
       <c r="P17">
-        <v>0.1687527426</v>
+        <v>0.16773092544</v>
       </c>
       <c r="Q17">
-        <v>0.1707527426</v>
+        <v>0.16973092544</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1482802413480118</v>
+        <v>0.149264318122664</v>
       </c>
       <c r="T17">
-        <v>1.335661089427489</v>
+        <v>1.348486908723218</v>
       </c>
       <c r="U17">
         <v>0.0518</v>
@@ -2707,7 +2707,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>12.00997642278781</v>
+        <v>11.25935289636357</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2715,22 +2715,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1318466672230377</v>
+        <v>0.1315945293002655</v>
       </c>
       <c r="C18">
-        <v>2.225472401623967</v>
+        <v>2.206839244903477</v>
       </c>
       <c r="D18">
-        <v>2.265112401623967</v>
+        <v>2.271769244903477</v>
       </c>
       <c r="E18">
-        <v>0.37564</v>
+        <v>0.40093</v>
       </c>
       <c r="F18">
-        <v>0.40464</v>
+        <v>0.42993</v>
       </c>
       <c r="G18">
         <v>0.365</v>
@@ -2751,28 +2751,28 @@
         <v>0.236</v>
       </c>
       <c r="M18">
-        <v>0.020960352</v>
+        <v>0.022270374</v>
       </c>
       <c r="N18">
-        <v>0.215039648</v>
+        <v>0.213729626</v>
       </c>
       <c r="O18">
-        <v>0.04730872256</v>
+        <v>0.04702051771999999</v>
       </c>
       <c r="P18">
-        <v>0.16773092544</v>
+        <v>0.16670910828</v>
       </c>
       <c r="Q18">
-        <v>0.16973092544</v>
+        <v>0.16870910828</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.149264318122664</v>
+        <v>0.1502721075906813</v>
       </c>
       <c r="T18">
-        <v>1.348486908723218</v>
+        <v>1.361621783905591</v>
       </c>
       <c r="U18">
         <v>0.0518</v>
@@ -2789,7 +2789,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>11.25935289636357</v>
+        <v>10.59703802010689</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2797,22 +2797,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1315945293002655</v>
+        <v>0.1313423913774932</v>
       </c>
       <c r="C19">
-        <v>2.206839244903477</v>
+        <v>2.188245330542469</v>
       </c>
       <c r="D19">
-        <v>2.271769244903477</v>
+        <v>2.278465330542469</v>
       </c>
       <c r="E19">
-        <v>0.40093</v>
+        <v>0.42622</v>
       </c>
       <c r="F19">
-        <v>0.42993</v>
+        <v>0.45522</v>
       </c>
       <c r="G19">
         <v>0.365</v>
@@ -2833,28 +2833,28 @@
         <v>0.236</v>
       </c>
       <c r="M19">
-        <v>0.022270374</v>
+        <v>0.023580396</v>
       </c>
       <c r="N19">
-        <v>0.213729626</v>
+        <v>0.212419604</v>
       </c>
       <c r="O19">
-        <v>0.04702051771999999</v>
+        <v>0.04673231287999999</v>
       </c>
       <c r="P19">
-        <v>0.16670910828</v>
+        <v>0.16568729112</v>
       </c>
       <c r="Q19">
-        <v>0.16870910828</v>
+        <v>0.16768729112</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1502721075906813</v>
+        <v>0.1513044772896259</v>
       </c>
       <c r="T19">
-        <v>1.361621783905591</v>
+        <v>1.37507702189729</v>
       </c>
       <c r="U19">
         <v>0.0518</v>
@@ -2871,7 +2871,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>10.59703802010689</v>
+        <v>10.00831368565651</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2879,22 +2879,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1313423913774932</v>
+        <v>0.131342193454721</v>
       </c>
       <c r="C20">
-        <v>2.188245330542469</v>
+        <v>2.1629606023289</v>
       </c>
       <c r="D20">
-        <v>2.278465330542469</v>
+        <v>2.2784706023289</v>
       </c>
       <c r="E20">
-        <v>0.4262199999999999</v>
+        <v>0.45151</v>
       </c>
       <c r="F20">
-        <v>0.45522</v>
+        <v>0.48051</v>
       </c>
       <c r="G20">
         <v>0.365</v>
@@ -2915,45 +2915,45 @@
         <v>0.236</v>
       </c>
       <c r="M20">
-        <v>0.023580396</v>
+        <v>0.025707285</v>
       </c>
       <c r="N20">
-        <v>0.212419604</v>
+        <v>0.210292715</v>
       </c>
       <c r="O20">
-        <v>0.04673231287999999</v>
+        <v>0.0462643973</v>
       </c>
       <c r="P20">
-        <v>0.16568729112</v>
+        <v>0.1640283177</v>
       </c>
       <c r="Q20">
-        <v>0.16768729112</v>
+        <v>0.1660283177</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1513044772896258</v>
+        <v>0.1523623375984209</v>
       </c>
       <c r="T20">
-        <v>1.375077021897289</v>
+        <v>1.388864487987549</v>
       </c>
       <c r="U20">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V20">
         <v>0.22</v>
       </c>
       <c r="W20">
-        <v>0.040404</v>
+        <v>0.04173</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y20">
-        <v>10.00831368565651</v>
+        <v>9.180277108220491</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2961,22 +2961,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.131342193454721</v>
+        <v>0.1311033155319487</v>
       </c>
       <c r="C21">
-        <v>2.1629606023289</v>
+        <v>2.144051084977058</v>
       </c>
       <c r="D21">
-        <v>2.2784706023289</v>
+        <v>2.284851084977058</v>
       </c>
       <c r="E21">
-        <v>0.45151</v>
+        <v>0.4768</v>
       </c>
       <c r="F21">
-        <v>0.48051</v>
+        <v>0.5058</v>
       </c>
       <c r="G21">
         <v>0.365</v>
@@ -2997,28 +2997,28 @@
         <v>0.236</v>
       </c>
       <c r="M21">
-        <v>0.025707285</v>
+        <v>0.0270603</v>
       </c>
       <c r="N21">
-        <v>0.210292715</v>
+        <v>0.2089397</v>
       </c>
       <c r="O21">
-        <v>0.0462643973</v>
+        <v>0.045966734</v>
       </c>
       <c r="P21">
-        <v>0.1640283177</v>
+        <v>0.162972966</v>
       </c>
       <c r="Q21">
-        <v>0.1660283177</v>
+        <v>0.164972966</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1523623375984209</v>
+        <v>0.1534466444149358</v>
       </c>
       <c r="T21">
-        <v>1.388864487987549</v>
+        <v>1.402996640730064</v>
       </c>
       <c r="U21">
         <v>0.0535</v>
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>9.180277108220491</v>
+        <v>8.721263252809464</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1311033155319487</v>
+        <v>0.1308644376091764</v>
       </c>
       <c r="C22">
-        <v>2.144051084977058</v>
+        <v>2.125177402963323</v>
       </c>
       <c r="D22">
-        <v>2.284851084977058</v>
+        <v>2.291267402963323</v>
       </c>
       <c r="E22">
-        <v>0.4768</v>
+        <v>0.50209</v>
       </c>
       <c r="F22">
-        <v>0.5058</v>
+        <v>0.5310900000000001</v>
       </c>
       <c r="G22">
         <v>0.365</v>
@@ -3079,28 +3079,28 @@
         <v>0.236</v>
       </c>
       <c r="M22">
-        <v>0.0270603</v>
+        <v>0.028413315</v>
       </c>
       <c r="N22">
-        <v>0.2089397</v>
+        <v>0.207586685</v>
       </c>
       <c r="O22">
-        <v>0.045966734</v>
+        <v>0.0456690707</v>
       </c>
       <c r="P22">
-        <v>0.162972966</v>
+        <v>0.1619176143</v>
       </c>
       <c r="Q22">
-        <v>0.164972966</v>
+        <v>0.1639176143</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1534466444149358</v>
+        <v>0.1545584020369322</v>
       </c>
       <c r="T22">
-        <v>1.402996640730064</v>
+        <v>1.417486569491378</v>
       </c>
       <c r="U22">
         <v>0.0535</v>
@@ -3117,7 +3117,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>8.721263252809464</v>
+        <v>8.305965002675681</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3125,22 +3125,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1308644376091764</v>
+        <v>0.1306255596864041</v>
       </c>
       <c r="C23">
-        <v>2.125177402963325</v>
+        <v>2.106339859036224</v>
       </c>
       <c r="D23">
-        <v>2.291267402963325</v>
+        <v>2.297719859036224</v>
       </c>
       <c r="E23">
-        <v>0.5020899999999999</v>
+        <v>0.52738</v>
       </c>
       <c r="F23">
-        <v>0.53109</v>
+        <v>0.55638</v>
       </c>
       <c r="G23">
         <v>0.365</v>
@@ -3161,28 +3161,28 @@
         <v>0.236</v>
       </c>
       <c r="M23">
-        <v>0.028413315</v>
+        <v>0.02976633</v>
       </c>
       <c r="N23">
-        <v>0.207586685</v>
+        <v>0.20623367</v>
       </c>
       <c r="O23">
-        <v>0.0456690707</v>
+        <v>0.04537140739999999</v>
       </c>
       <c r="P23">
-        <v>0.1619176143</v>
+        <v>0.1608622626</v>
       </c>
       <c r="Q23">
-        <v>0.1639176143</v>
+        <v>0.1628622626</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1545584020369321</v>
+        <v>0.1556986662646207</v>
       </c>
       <c r="T23">
-        <v>1.417486569491378</v>
+        <v>1.432348034887597</v>
       </c>
       <c r="U23">
         <v>0.0535</v>
@@ -3199,7 +3199,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>8.305965002675682</v>
+        <v>7.928421138917696</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3207,22 +3207,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1306255596864041</v>
+        <v>0.1305302017636319</v>
       </c>
       <c r="C24">
-        <v>2.106339859036224</v>
+        <v>2.08363578221721</v>
       </c>
       <c r="D24">
-        <v>2.297719859036224</v>
+        <v>2.30030578221721</v>
       </c>
       <c r="E24">
-        <v>0.52738</v>
+        <v>0.55267</v>
       </c>
       <c r="F24">
-        <v>0.55638</v>
+        <v>0.58167</v>
       </c>
       <c r="G24">
         <v>0.365</v>
@@ -3243,45 +3243,45 @@
         <v>0.236</v>
       </c>
       <c r="M24">
-        <v>0.02976633</v>
+        <v>0.031584681</v>
       </c>
       <c r="N24">
-        <v>0.20623367</v>
+        <v>0.204415319</v>
       </c>
       <c r="O24">
-        <v>0.04537140739999999</v>
+        <v>0.04497137018</v>
       </c>
       <c r="P24">
-        <v>0.1608622626</v>
+        <v>0.15944394882</v>
       </c>
       <c r="Q24">
-        <v>0.1628622626</v>
+        <v>0.16144394882</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1556986662646207</v>
+        <v>0.1568685477449765</v>
       </c>
       <c r="T24">
-        <v>1.432348034887597</v>
+        <v>1.44759551237203</v>
       </c>
       <c r="U24">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V24">
         <v>0.22</v>
       </c>
       <c r="W24">
-        <v>0.04173</v>
+        <v>0.042354</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y24">
-        <v>7.928421138917696</v>
+        <v>7.471976683886722</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3289,22 +3289,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1305302017636319</v>
+        <v>0.1302975638408596</v>
       </c>
       <c r="C25">
-        <v>2.08363578221721</v>
+        <v>2.064678963134993</v>
       </c>
       <c r="D25">
-        <v>2.30030578221721</v>
+        <v>2.306638963134993</v>
       </c>
       <c r="E25">
-        <v>0.55267</v>
+        <v>0.57796</v>
       </c>
       <c r="F25">
-        <v>0.58167</v>
+        <v>0.6069600000000001</v>
       </c>
       <c r="G25">
         <v>0.365</v>
@@ -3325,28 +3325,28 @@
         <v>0.236</v>
       </c>
       <c r="M25">
-        <v>0.031584681</v>
+        <v>0.032957928</v>
       </c>
       <c r="N25">
-        <v>0.204415319</v>
+        <v>0.203042072</v>
       </c>
       <c r="O25">
-        <v>0.04497137018</v>
+        <v>0.04466925584</v>
       </c>
       <c r="P25">
-        <v>0.15944394882</v>
+        <v>0.15837281616</v>
       </c>
       <c r="Q25">
-        <v>0.16144394882</v>
+        <v>0.16037281616</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1568685477449765</v>
+        <v>0.1580692155800784</v>
       </c>
       <c r="T25">
-        <v>1.44759551237203</v>
+        <v>1.463244239263948</v>
       </c>
       <c r="U25">
         <v>0.0543</v>
@@ -3363,7 +3363,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>7.471976683886722</v>
+        <v>7.160644322058109</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3371,22 +3371,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1302975638408596</v>
+        <v>0.1300649259180873</v>
       </c>
       <c r="C26">
-        <v>2.064678963134993</v>
+        <v>2.04575711324161</v>
       </c>
       <c r="D26">
-        <v>2.306638963134993</v>
+        <v>2.31300711324161</v>
       </c>
       <c r="E26">
-        <v>0.5779599999999999</v>
+        <v>0.60325</v>
       </c>
       <c r="F26">
-        <v>0.6069599999999999</v>
+        <v>0.63225</v>
       </c>
       <c r="G26">
         <v>0.365</v>
@@ -3407,28 +3407,28 @@
         <v>0.236</v>
       </c>
       <c r="M26">
-        <v>0.032957928</v>
+        <v>0.034331175</v>
       </c>
       <c r="N26">
-        <v>0.203042072</v>
+        <v>0.201668825</v>
       </c>
       <c r="O26">
-        <v>0.04466925584</v>
+        <v>0.0443671415</v>
       </c>
       <c r="P26">
-        <v>0.15837281616</v>
+        <v>0.1573016835</v>
       </c>
       <c r="Q26">
-        <v>0.16037281616</v>
+        <v>0.1593016835</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1580692155800784</v>
+        <v>0.1593019012241164</v>
       </c>
       <c r="T26">
-        <v>1.463244239263948</v>
+        <v>1.47931026553965</v>
       </c>
       <c r="U26">
         <v>0.0543</v>
@@ -3445,7 +3445,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>7.16064432205811</v>
+        <v>6.874218549175786</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3453,22 +3453,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1300649259180873</v>
+        <v>0.1298322879953151</v>
       </c>
       <c r="C27">
-        <v>2.04575711324161</v>
+        <v>2.026870522966834</v>
       </c>
       <c r="D27">
-        <v>2.31300711324161</v>
+        <v>2.319410522966834</v>
       </c>
       <c r="E27">
-        <v>0.60325</v>
+        <v>0.62854</v>
       </c>
       <c r="F27">
-        <v>0.63225</v>
+        <v>0.65754</v>
       </c>
       <c r="G27">
         <v>0.365</v>
@@ -3489,28 +3489,28 @@
         <v>0.236</v>
       </c>
       <c r="M27">
-        <v>0.034331175</v>
+        <v>0.035704422</v>
       </c>
       <c r="N27">
-        <v>0.201668825</v>
+        <v>0.200295578</v>
       </c>
       <c r="O27">
-        <v>0.0443671415</v>
+        <v>0.04406502715999999</v>
       </c>
       <c r="P27">
-        <v>0.1573016835</v>
+        <v>0.15623055084</v>
       </c>
       <c r="Q27">
-        <v>0.1593016835</v>
+        <v>0.15823055084</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1593019012241164</v>
+        <v>0.1605679026963717</v>
       </c>
       <c r="T27">
-        <v>1.47931026553965</v>
+        <v>1.495810508741722</v>
       </c>
       <c r="U27">
         <v>0.0543</v>
@@ -3527,7 +3527,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>6.874218549175786</v>
+        <v>6.609825528053639</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3535,22 +3535,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1298322879953151</v>
+        <v>0.1295996500725428</v>
       </c>
       <c r="C28">
-        <v>2.026870522966834</v>
+        <v>2.00801948596551</v>
       </c>
       <c r="D28">
-        <v>2.319410522966834</v>
+        <v>2.325849485965509</v>
       </c>
       <c r="E28">
-        <v>0.62854</v>
+        <v>0.65383</v>
       </c>
       <c r="F28">
-        <v>0.65754</v>
+        <v>0.68283</v>
       </c>
       <c r="G28">
         <v>0.365</v>
@@ -3571,28 +3571,28 @@
         <v>0.236</v>
       </c>
       <c r="M28">
-        <v>0.035704422</v>
+        <v>0.037077669</v>
       </c>
       <c r="N28">
-        <v>0.200295578</v>
+        <v>0.198922331</v>
       </c>
       <c r="O28">
-        <v>0.04406502715999999</v>
+        <v>0.04376291281999999</v>
       </c>
       <c r="P28">
-        <v>0.15623055084</v>
+        <v>0.15515941818</v>
       </c>
       <c r="Q28">
-        <v>0.15823055084</v>
+        <v>0.15715941818</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1605679026963717</v>
+        <v>0.1618685891404696</v>
       </c>
       <c r="T28">
-        <v>1.495810508741722</v>
+        <v>1.512762813401386</v>
       </c>
       <c r="U28">
         <v>0.0543</v>
@@ -3609,7 +3609,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>6.609825528053639</v>
+        <v>6.365017175162764</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3617,22 +3617,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1295996500725428</v>
+        <v>0.1293670121497706</v>
       </c>
       <c r="C29">
-        <v>2.00801948596551</v>
+        <v>1.989204299162447</v>
       </c>
       <c r="D29">
-        <v>2.325849485965509</v>
+        <v>2.332324299162447</v>
       </c>
       <c r="E29">
-        <v>0.65383</v>
+        <v>0.6791200000000001</v>
       </c>
       <c r="F29">
-        <v>0.68283</v>
+        <v>0.7081200000000001</v>
       </c>
       <c r="G29">
         <v>0.365</v>
@@ -3653,28 +3653,28 @@
         <v>0.236</v>
       </c>
       <c r="M29">
-        <v>0.037077669</v>
+        <v>0.03845091600000001</v>
       </c>
       <c r="N29">
-        <v>0.198922331</v>
+        <v>0.197549084</v>
       </c>
       <c r="O29">
-        <v>0.04376291281999999</v>
+        <v>0.04346079848</v>
       </c>
       <c r="P29">
-        <v>0.15515941818</v>
+        <v>0.15408828552</v>
       </c>
       <c r="Q29">
-        <v>0.15715941818</v>
+        <v>0.15608828552</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1618685891404696</v>
+        <v>0.1632054057635702</v>
       </c>
       <c r="T29">
-        <v>1.512762813401386</v>
+        <v>1.530186015412706</v>
       </c>
       <c r="U29">
         <v>0.0543</v>
@@ -3691,7 +3691,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>6.365017175162764</v>
+        <v>6.137695133192664</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3699,22 +3699,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1293670121497706</v>
+        <v>0.1293605742269983</v>
       </c>
       <c r="C30">
-        <v>1.989204299162447</v>
+        <v>1.964093993041491</v>
       </c>
       <c r="D30">
-        <v>2.332324299162447</v>
+        <v>2.332503993041491</v>
       </c>
       <c r="E30">
-        <v>0.6791200000000001</v>
+        <v>0.7044100000000001</v>
       </c>
       <c r="F30">
-        <v>0.7081200000000001</v>
+        <v>0.7334100000000001</v>
       </c>
       <c r="G30">
         <v>0.365</v>
@@ -3735,45 +3735,45 @@
         <v>0.236</v>
       </c>
       <c r="M30">
-        <v>0.03845091600000001</v>
+        <v>0.04055757300000001</v>
       </c>
       <c r="N30">
-        <v>0.197549084</v>
+        <v>0.195442427</v>
       </c>
       <c r="O30">
-        <v>0.04346079848</v>
+        <v>0.04299733393999999</v>
       </c>
       <c r="P30">
-        <v>0.15408828552</v>
+        <v>0.15244509306</v>
       </c>
       <c r="Q30">
-        <v>0.15608828552</v>
+        <v>0.15444509306</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1632054057635702</v>
+        <v>0.1645798791929553</v>
       </c>
       <c r="T30">
-        <v>1.530186015412706</v>
+        <v>1.548100011846881</v>
       </c>
       <c r="U30">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V30">
         <v>0.22</v>
       </c>
       <c r="W30">
-        <v>0.042354</v>
+        <v>0.04313400000000001</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y30">
-        <v>6.137695133192664</v>
+        <v>5.818888620381697</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3781,22 +3781,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1293605742269983</v>
+        <v>0.129135736304226</v>
       </c>
       <c r="C31">
-        <v>1.964093993041491</v>
+        <v>1.945097035809349</v>
       </c>
       <c r="D31">
-        <v>2.332503993041491</v>
+        <v>2.338797035809349</v>
       </c>
       <c r="E31">
-        <v>0.7044099999999999</v>
+        <v>0.7296999999999999</v>
       </c>
       <c r="F31">
-        <v>0.7334099999999999</v>
+        <v>0.7586999999999999</v>
       </c>
       <c r="G31">
         <v>0.365</v>
@@ -3817,28 +3817,28 @@
         <v>0.236</v>
       </c>
       <c r="M31">
-        <v>0.04055757299999999</v>
+        <v>0.04195611</v>
       </c>
       <c r="N31">
-        <v>0.195442427</v>
+        <v>0.19404389</v>
       </c>
       <c r="O31">
-        <v>0.04299733394</v>
+        <v>0.0426896558</v>
       </c>
       <c r="P31">
-        <v>0.15244509306</v>
+        <v>0.1513542342</v>
       </c>
       <c r="Q31">
-        <v>0.15444509306</v>
+        <v>0.1533542342</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1645798791929553</v>
+        <v>0.1659936232917514</v>
       </c>
       <c r="T31">
-        <v>1.548100011846881</v>
+        <v>1.566525836750604</v>
       </c>
       <c r="U31">
         <v>0.0553</v>
@@ -3855,7 +3855,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>5.818888620381699</v>
+        <v>5.624925666368974</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3863,22 +3863,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.129135736304226</v>
+        <v>0.1289108983814538</v>
       </c>
       <c r="C32">
-        <v>1.945097035809349</v>
+        <v>1.926134127412953</v>
       </c>
       <c r="D32">
-        <v>2.338797035809349</v>
+        <v>2.345124127412953</v>
       </c>
       <c r="E32">
-        <v>0.7296999999999999</v>
+        <v>0.7549899999999999</v>
       </c>
       <c r="F32">
-        <v>0.7586999999999999</v>
+        <v>0.78399</v>
       </c>
       <c r="G32">
         <v>0.365</v>
@@ -3899,28 +3899,28 @@
         <v>0.236</v>
       </c>
       <c r="M32">
-        <v>0.04195611</v>
+        <v>0.043354647</v>
       </c>
       <c r="N32">
-        <v>0.19404389</v>
+        <v>0.192645353</v>
       </c>
       <c r="O32">
-        <v>0.0426896558</v>
+        <v>0.04238197766</v>
       </c>
       <c r="P32">
-        <v>0.1513542342</v>
+        <v>0.15026337534</v>
       </c>
       <c r="Q32">
-        <v>0.1533542342</v>
+        <v>0.15226337534</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1659936232917514</v>
+        <v>0.1674483454803677</v>
       </c>
       <c r="T32">
-        <v>1.566525836750604</v>
+        <v>1.585485743535594</v>
       </c>
       <c r="U32">
         <v>0.0553</v>
@@ -3937,7 +3937,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>5.624925666368974</v>
+        <v>5.443476451324814</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3945,22 +3945,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1289108983814538</v>
+        <v>0.1286860604586814</v>
       </c>
       <c r="C33">
-        <v>1.926134127412953</v>
+        <v>1.907205544936392</v>
       </c>
       <c r="D33">
-        <v>2.345124127412953</v>
+        <v>2.351485544936393</v>
       </c>
       <c r="E33">
-        <v>0.7549899999999999</v>
+        <v>0.78028</v>
       </c>
       <c r="F33">
-        <v>0.78399</v>
+        <v>0.80928</v>
       </c>
       <c r="G33">
         <v>0.365</v>
@@ -3981,28 +3981,28 @@
         <v>0.236</v>
       </c>
       <c r="M33">
-        <v>0.043354647</v>
+        <v>0.044753184</v>
       </c>
       <c r="N33">
-        <v>0.192645353</v>
+        <v>0.191246816</v>
       </c>
       <c r="O33">
-        <v>0.04238197766</v>
+        <v>0.04207429952</v>
       </c>
       <c r="P33">
-        <v>0.15026337534</v>
+        <v>0.14917251648</v>
       </c>
       <c r="Q33">
-        <v>0.15226337534</v>
+        <v>0.15117251648</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1674483454803677</v>
+        <v>0.168945853615708</v>
       </c>
       <c r="T33">
-        <v>1.585485743535594</v>
+        <v>1.60500329463779</v>
       </c>
       <c r="U33">
         <v>0.0553</v>
@@ -4019,7 +4019,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>5.443476451324814</v>
+        <v>5.273367812220913</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4027,22 +4027,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1286860604586814</v>
+        <v>0.1284612225359092</v>
       </c>
       <c r="C34">
-        <v>1.907205544936392</v>
+        <v>1.88831156847842</v>
       </c>
       <c r="D34">
-        <v>2.351485544936393</v>
+        <v>2.35788156847842</v>
       </c>
       <c r="E34">
-        <v>0.78028</v>
+        <v>0.80557</v>
       </c>
       <c r="F34">
-        <v>0.80928</v>
+        <v>0.83457</v>
       </c>
       <c r="G34">
         <v>0.365</v>
@@ -4063,28 +4063,28 @@
         <v>0.236</v>
       </c>
       <c r="M34">
-        <v>0.044753184</v>
+        <v>0.04615172100000001</v>
       </c>
       <c r="N34">
-        <v>0.191246816</v>
+        <v>0.189848279</v>
       </c>
       <c r="O34">
-        <v>0.04207429952</v>
+        <v>0.04176662137999999</v>
       </c>
       <c r="P34">
-        <v>0.14917251648</v>
+        <v>0.14808165762</v>
       </c>
       <c r="Q34">
-        <v>0.15117251648</v>
+        <v>0.15008165762</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.168945853615708</v>
+        <v>0.1704880634864316</v>
       </c>
       <c r="T34">
-        <v>1.60500329463779</v>
+        <v>1.625103459205723</v>
       </c>
       <c r="U34">
         <v>0.0553</v>
@@ -4101,7 +4101,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>5.273367812220913</v>
+        <v>5.113568787608158</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1284612225359092</v>
+        <v>0.1282363846131369</v>
       </c>
       <c r="C35">
-        <v>1.88831156847842</v>
+        <v>1.86945248119357</v>
       </c>
       <c r="D35">
-        <v>2.35788156847842</v>
+        <v>2.364312481193571</v>
       </c>
       <c r="E35">
-        <v>0.80557</v>
+        <v>0.83086</v>
       </c>
       <c r="F35">
-        <v>0.83457</v>
+        <v>0.8598600000000001</v>
       </c>
       <c r="G35">
         <v>0.365</v>
@@ -4145,28 +4145,28 @@
         <v>0.236</v>
       </c>
       <c r="M35">
-        <v>0.04615172100000001</v>
+        <v>0.047550258</v>
       </c>
       <c r="N35">
-        <v>0.189848279</v>
+        <v>0.188449742</v>
       </c>
       <c r="O35">
-        <v>0.04176662137999999</v>
+        <v>0.04145894324</v>
       </c>
       <c r="P35">
-        <v>0.14808165762</v>
+        <v>0.14699079876</v>
       </c>
       <c r="Q35">
-        <v>0.15008165762</v>
+        <v>0.14899079876</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1704880634864316</v>
+        <v>0.1720770069896014</v>
       </c>
       <c r="T35">
-        <v>1.625103459205723</v>
+        <v>1.645812719669653</v>
       </c>
       <c r="U35">
         <v>0.0553</v>
@@ -4183,7 +4183,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>5.113568787608158</v>
+        <v>4.963169705619682</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4191,22 +4191,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1282363846131369</v>
+        <v>0.1280115466903647</v>
       </c>
       <c r="C36">
-        <v>1.86945248119357</v>
+        <v>1.850628569333941</v>
       </c>
       <c r="D36">
-        <v>2.364312481193571</v>
+        <v>2.370778569333942</v>
       </c>
       <c r="E36">
-        <v>0.83086</v>
+        <v>0.8561500000000001</v>
       </c>
       <c r="F36">
-        <v>0.8598600000000001</v>
+        <v>0.8851500000000001</v>
       </c>
       <c r="G36">
         <v>0.365</v>
@@ -4227,28 +4227,28 @@
         <v>0.236</v>
       </c>
       <c r="M36">
-        <v>0.047550258</v>
+        <v>0.04894879500000001</v>
       </c>
       <c r="N36">
-        <v>0.188449742</v>
+        <v>0.187051205</v>
       </c>
       <c r="O36">
-        <v>0.04145894324</v>
+        <v>0.04115126509999999</v>
       </c>
       <c r="P36">
-        <v>0.14699079876</v>
+        <v>0.1458999399</v>
       </c>
       <c r="Q36">
-        <v>0.14899079876</v>
+        <v>0.1478999399</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1720770069896014</v>
+        <v>0.1737148410620995</v>
       </c>
       <c r="T36">
-        <v>1.645812719669653</v>
+        <v>1.667159188147859</v>
       </c>
       <c r="U36">
         <v>0.0553</v>
@@ -4265,7 +4265,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>4.963169705619682</v>
+        <v>4.821364856887691</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4273,22 +4273,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1280115466903647</v>
+        <v>0.1277867087675924</v>
       </c>
       <c r="C37">
-        <v>1.850628569333941</v>
+        <v>1.831840122291668</v>
       </c>
       <c r="D37">
-        <v>2.370778569333942</v>
+        <v>2.377280122291667</v>
       </c>
       <c r="E37">
-        <v>0.8561500000000001</v>
+        <v>0.88144</v>
       </c>
       <c r="F37">
-        <v>0.8851500000000001</v>
+        <v>0.91044</v>
       </c>
       <c r="G37">
         <v>0.365</v>
@@ -4309,28 +4309,28 @@
         <v>0.236</v>
       </c>
       <c r="M37">
-        <v>0.04894879500000001</v>
+        <v>0.050347332</v>
       </c>
       <c r="N37">
-        <v>0.187051205</v>
+        <v>0.185652668</v>
       </c>
       <c r="O37">
-        <v>0.04115126509999999</v>
+        <v>0.04084358696</v>
       </c>
       <c r="P37">
-        <v>0.1458999399</v>
+        <v>0.14480908104</v>
       </c>
       <c r="Q37">
-        <v>0.1478999399</v>
+        <v>0.14680908104</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1737148410620995</v>
+        <v>0.1754038574493631</v>
       </c>
       <c r="T37">
-        <v>1.667159188147859</v>
+        <v>1.689172733766009</v>
       </c>
       <c r="U37">
         <v>0.0553</v>
@@ -4347,7 +4347,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>4.821364856887691</v>
+        <v>4.687438055307479</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4355,22 +4355,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1277867087675924</v>
+        <v>0.1275618708448201</v>
       </c>
       <c r="C38">
-        <v>1.831840122291667</v>
+        <v>1.813087432642091</v>
       </c>
       <c r="D38">
-        <v>2.377280122291666</v>
+        <v>2.383817432642091</v>
       </c>
       <c r="E38">
-        <v>0.8814399999999999</v>
+        <v>0.9067299999999999</v>
       </c>
       <c r="F38">
-        <v>0.9104399999999999</v>
+        <v>0.93573</v>
       </c>
       <c r="G38">
         <v>0.365</v>
@@ -4391,28 +4391,28 @@
         <v>0.236</v>
       </c>
       <c r="M38">
-        <v>0.05034733199999999</v>
+        <v>0.051745869</v>
       </c>
       <c r="N38">
-        <v>0.185652668</v>
+        <v>0.184254131</v>
       </c>
       <c r="O38">
-        <v>0.04084358696</v>
+        <v>0.04053590882</v>
       </c>
       <c r="P38">
-        <v>0.14480908104</v>
+        <v>0.14371822218</v>
       </c>
       <c r="Q38">
-        <v>0.14680908104</v>
+        <v>0.14571822218</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1754038574493631</v>
+        <v>0.1771464934044764</v>
       </c>
       <c r="T38">
-        <v>1.689172733766009</v>
+        <v>1.711885122102195</v>
       </c>
       <c r="U38">
         <v>0.0553</v>
@@ -4429,7 +4429,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>4.68743805530748</v>
+        <v>4.560750540299169</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4437,22 +4437,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1275618708448201</v>
+        <v>0.1280780329220479</v>
       </c>
       <c r="C39">
-        <v>1.813087432642091</v>
+        <v>1.772842819435307</v>
       </c>
       <c r="D39">
-        <v>2.383817432642091</v>
+        <v>2.368862819435307</v>
       </c>
       <c r="E39">
-        <v>0.9067299999999999</v>
+        <v>0.93202</v>
       </c>
       <c r="F39">
-        <v>0.93573</v>
+        <v>0.96102</v>
       </c>
       <c r="G39">
         <v>0.365</v>
@@ -4473,45 +4473,45 @@
         <v>0.236</v>
       </c>
       <c r="M39">
-        <v>0.051745869</v>
+        <v>0.055546956</v>
       </c>
       <c r="N39">
-        <v>0.184254131</v>
+        <v>0.180453044</v>
       </c>
       <c r="O39">
-        <v>0.04053590882</v>
+        <v>0.03969966967999999</v>
       </c>
       <c r="P39">
-        <v>0.14371822218</v>
+        <v>0.14075337432</v>
       </c>
       <c r="Q39">
-        <v>0.14571822218</v>
+        <v>0.14275337432</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1771464934044764</v>
+        <v>0.1789453434226578</v>
       </c>
       <c r="T39">
-        <v>1.711885122102195</v>
+        <v>1.735330168126645</v>
       </c>
       <c r="U39">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V39">
         <v>0.22</v>
       </c>
       <c r="W39">
-        <v>0.04313400000000001</v>
+        <v>0.04508400000000001</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y39">
-        <v>4.560750540299169</v>
+        <v>4.24865765821623</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4519,22 +4519,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1280780329220479</v>
+        <v>0.1278726949992756</v>
       </c>
       <c r="C40">
-        <v>1.772842819435307</v>
+        <v>1.753479484456841</v>
       </c>
       <c r="D40">
-        <v>2.368862819435307</v>
+        <v>2.374789484456841</v>
       </c>
       <c r="E40">
-        <v>0.93202</v>
+        <v>0.95731</v>
       </c>
       <c r="F40">
-        <v>0.96102</v>
+        <v>0.98631</v>
       </c>
       <c r="G40">
         <v>0.365</v>
@@ -4555,28 +4555,28 @@
         <v>0.236</v>
       </c>
       <c r="M40">
-        <v>0.055546956</v>
+        <v>0.05700871800000001</v>
       </c>
       <c r="N40">
-        <v>0.180453044</v>
+        <v>0.178991282</v>
       </c>
       <c r="O40">
-        <v>0.03969966967999999</v>
+        <v>0.03937808203999999</v>
       </c>
       <c r="P40">
-        <v>0.14075337432</v>
+        <v>0.13961319996</v>
       </c>
       <c r="Q40">
-        <v>0.14275337432</v>
+        <v>0.14161319996</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1789453434226578</v>
+        <v>0.18080317212996</v>
       </c>
       <c r="T40">
-        <v>1.735330168126645</v>
+        <v>1.759543904184683</v>
       </c>
       <c r="U40">
         <v>0.0578</v>
@@ -4593,7 +4593,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>4.24865765821623</v>
+        <v>4.139717718261967</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4601,22 +4601,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1278726949992756</v>
+        <v>0.1276673570765033</v>
       </c>
       <c r="C41">
-        <v>1.753479484456841</v>
+        <v>1.734145879742745</v>
       </c>
       <c r="D41">
-        <v>2.374789484456841</v>
+        <v>2.380745879742745</v>
       </c>
       <c r="E41">
-        <v>0.95731</v>
+        <v>0.9826</v>
       </c>
       <c r="F41">
-        <v>0.98631</v>
+        <v>1.0116</v>
       </c>
       <c r="G41">
         <v>0.365</v>
@@ -4637,28 +4637,28 @@
         <v>0.236</v>
       </c>
       <c r="M41">
-        <v>0.05700871800000001</v>
+        <v>0.05847048000000001</v>
       </c>
       <c r="N41">
-        <v>0.178991282</v>
+        <v>0.17752952</v>
       </c>
       <c r="O41">
-        <v>0.03937808203999999</v>
+        <v>0.0390564944</v>
       </c>
       <c r="P41">
-        <v>0.13961319996</v>
+        <v>0.1384730256</v>
       </c>
       <c r="Q41">
-        <v>0.14161319996</v>
+        <v>0.1404730256</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.18080317212996</v>
+        <v>0.1827229284608389</v>
       </c>
       <c r="T41">
-        <v>1.759543904184683</v>
+        <v>1.78456476477799</v>
       </c>
       <c r="U41">
         <v>0.0578</v>
@@ -4675,7 +4675,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>4.139717718261967</v>
+        <v>4.036224775305419</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4683,22 +4683,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1276673570765033</v>
+        <v>0.1285813191537311</v>
       </c>
       <c r="C42">
-        <v>1.734145879742745</v>
+        <v>1.68257082567686</v>
       </c>
       <c r="D42">
-        <v>2.380745879742745</v>
+        <v>2.35446082567686</v>
       </c>
       <c r="E42">
-        <v>0.9826</v>
+        <v>1.00789</v>
       </c>
       <c r="F42">
-        <v>1.0116</v>
+        <v>1.03689</v>
       </c>
       <c r="G42">
         <v>0.365</v>
@@ -4719,45 +4719,45 @@
         <v>0.236</v>
       </c>
       <c r="M42">
-        <v>0.05847048000000001</v>
+        <v>0.063561357</v>
       </c>
       <c r="N42">
-        <v>0.17752952</v>
+        <v>0.172438643</v>
       </c>
       <c r="O42">
-        <v>0.0390564944</v>
+        <v>0.03793650146</v>
       </c>
       <c r="P42">
-        <v>0.1384730256</v>
+        <v>0.13450214154</v>
       </c>
       <c r="Q42">
-        <v>0.1404730256</v>
+        <v>0.13650214154</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1827229284608389</v>
+        <v>0.1847077612775103</v>
       </c>
       <c r="T42">
-        <v>1.78456476477799</v>
+        <v>1.810433790137171</v>
       </c>
       <c r="U42">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V42">
         <v>0.22</v>
       </c>
       <c r="W42">
-        <v>0.04508400000000001</v>
+        <v>0.047814</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y42">
-        <v>4.036224775305419</v>
+        <v>3.712947789959865</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4765,22 +4765,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1285813191537311</v>
+        <v>0.1284032812309588</v>
       </c>
       <c r="C43">
-        <v>1.68257082567686</v>
+        <v>1.662355482620332</v>
       </c>
       <c r="D43">
-        <v>2.35446082567686</v>
+        <v>2.359535482620331</v>
       </c>
       <c r="E43">
-        <v>1.00789</v>
+        <v>1.03318</v>
       </c>
       <c r="F43">
-        <v>1.03689</v>
+        <v>1.06218</v>
       </c>
       <c r="G43">
         <v>0.365</v>
@@ -4801,28 +4801,28 @@
         <v>0.236</v>
       </c>
       <c r="M43">
-        <v>0.063561357</v>
+        <v>0.065111634</v>
       </c>
       <c r="N43">
-        <v>0.172438643</v>
+        <v>0.170888366</v>
       </c>
       <c r="O43">
-        <v>0.03793650146</v>
+        <v>0.03759544052</v>
       </c>
       <c r="P43">
-        <v>0.13450214154</v>
+        <v>0.13329292548</v>
       </c>
       <c r="Q43">
-        <v>0.13650214154</v>
+        <v>0.13529292548</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1847077612775103</v>
+        <v>0.1867610366051014</v>
       </c>
       <c r="T43">
-        <v>1.810433790137171</v>
+        <v>1.837194850853566</v>
       </c>
       <c r="U43">
         <v>0.0613</v>
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>3.712947789959865</v>
+        <v>3.624544271151297</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4847,22 +4847,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1284032812309588</v>
+        <v>0.1282252433081865</v>
       </c>
       <c r="C44">
-        <v>1.662355482620331</v>
+        <v>1.642162062007577</v>
       </c>
       <c r="D44">
-        <v>2.359535482620331</v>
+        <v>2.364632062007576</v>
       </c>
       <c r="E44">
-        <v>1.03318</v>
+        <v>1.05847</v>
       </c>
       <c r="F44">
-        <v>1.06218</v>
+        <v>1.08747</v>
       </c>
       <c r="G44">
         <v>0.365</v>
@@ -4883,28 +4883,28 @@
         <v>0.236</v>
       </c>
       <c r="M44">
-        <v>0.06511163399999999</v>
+        <v>0.06666191099999999</v>
       </c>
       <c r="N44">
-        <v>0.170888366</v>
+        <v>0.169338089</v>
       </c>
       <c r="O44">
-        <v>0.03759544052</v>
+        <v>0.03725437958</v>
       </c>
       <c r="P44">
-        <v>0.13329292548</v>
+        <v>0.13208370942</v>
       </c>
       <c r="Q44">
-        <v>0.13529292548</v>
+        <v>0.13408370942</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1867610366051014</v>
+        <v>0.188886356681029</v>
       </c>
       <c r="T44">
-        <v>1.837194850853566</v>
+        <v>1.864894896156501</v>
       </c>
       <c r="U44">
         <v>0.0613</v>
@@ -4921,7 +4921,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>3.624544271151298</v>
+        <v>3.540252543915221</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4929,22 +4929,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1282252433081865</v>
+        <v>0.1290081653854143</v>
       </c>
       <c r="C45">
-        <v>1.642162062007577</v>
+        <v>1.594622771480726</v>
       </c>
       <c r="D45">
-        <v>2.364632062007576</v>
+        <v>2.342382771480726</v>
       </c>
       <c r="E45">
-        <v>1.05847</v>
+        <v>1.08376</v>
       </c>
       <c r="F45">
-        <v>1.08747</v>
+        <v>1.11276</v>
       </c>
       <c r="G45">
         <v>0.365</v>
@@ -4965,45 +4965,45 @@
         <v>0.236</v>
       </c>
       <c r="M45">
-        <v>0.06666191099999999</v>
+        <v>0.07132791600000001</v>
       </c>
       <c r="N45">
-        <v>0.169338089</v>
+        <v>0.164672084</v>
       </c>
       <c r="O45">
-        <v>0.03725437958</v>
+        <v>0.03622785848</v>
       </c>
       <c r="P45">
-        <v>0.13208370942</v>
+        <v>0.12844422552</v>
       </c>
       <c r="Q45">
-        <v>0.13408370942</v>
+        <v>0.13044422552</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.188886356681029</v>
+        <v>0.1910875810453826</v>
       </c>
       <c r="T45">
-        <v>1.864894896156501</v>
+        <v>1.893584228791683</v>
       </c>
       <c r="U45">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V45">
         <v>0.22</v>
       </c>
       <c r="W45">
-        <v>0.047814</v>
+        <v>0.04999800000000001</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y45">
-        <v>3.540252543915221</v>
+        <v>3.308662487769865</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5011,22 +5011,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1290081653854143</v>
+        <v>0.128851967462642</v>
       </c>
       <c r="C46">
-        <v>1.594622771480726</v>
+        <v>1.573738149636366</v>
       </c>
       <c r="D46">
-        <v>2.342382771480726</v>
+        <v>2.346788149636366</v>
       </c>
       <c r="E46">
-        <v>1.08376</v>
+        <v>1.10905</v>
       </c>
       <c r="F46">
-        <v>1.11276</v>
+        <v>1.13805</v>
       </c>
       <c r="G46">
         <v>0.365</v>
@@ -5047,28 +5047,28 @@
         <v>0.236</v>
       </c>
       <c r="M46">
-        <v>0.07132791600000001</v>
+        <v>0.07294900500000001</v>
       </c>
       <c r="N46">
-        <v>0.164672084</v>
+        <v>0.163050995</v>
       </c>
       <c r="O46">
-        <v>0.03622785848</v>
+        <v>0.03587121889999999</v>
       </c>
       <c r="P46">
-        <v>0.12844422552</v>
+        <v>0.1271797761</v>
       </c>
       <c r="Q46">
-        <v>0.13044422552</v>
+        <v>0.1291797761</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1910875810453826</v>
+        <v>0.1933688499320764</v>
       </c>
       <c r="T46">
-        <v>1.893584228791683</v>
+        <v>1.923316809886326</v>
       </c>
       <c r="U46">
         <v>0.0641</v>
@@ -5085,7 +5085,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>3.308662487769865</v>
+        <v>3.235136654708312</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5093,22 +5093,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.128851967462642</v>
+        <v>0.1286957695398697</v>
       </c>
       <c r="C47">
-        <v>1.573738149636366</v>
+        <v>1.552870129626352</v>
       </c>
       <c r="D47">
-        <v>2.346788149636366</v>
+        <v>2.351210129626352</v>
       </c>
       <c r="E47">
-        <v>1.10905</v>
+        <v>1.13434</v>
       </c>
       <c r="F47">
-        <v>1.13805</v>
+        <v>1.16334</v>
       </c>
       <c r="G47">
         <v>0.365</v>
@@ -5129,28 +5129,28 @@
         <v>0.236</v>
       </c>
       <c r="M47">
-        <v>0.07294900500000001</v>
+        <v>0.074570094</v>
       </c>
       <c r="N47">
-        <v>0.163050995</v>
+        <v>0.161429906</v>
       </c>
       <c r="O47">
-        <v>0.03587121889999999</v>
+        <v>0.03551457932</v>
       </c>
       <c r="P47">
-        <v>0.1271797761</v>
+        <v>0.12591532668</v>
       </c>
       <c r="Q47">
-        <v>0.1291797761</v>
+        <v>0.12791532668</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1933688499320764</v>
+        <v>0.195734610259018</v>
       </c>
       <c r="T47">
-        <v>1.923316809886326</v>
+        <v>1.954150597688179</v>
       </c>
       <c r="U47">
         <v>0.0641</v>
@@ -5167,7 +5167,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>3.235136654708312</v>
+        <v>3.164807596997262</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1286957695398697</v>
+        <v>0.1285395716170975</v>
       </c>
       <c r="C48">
-        <v>1.552870129626352</v>
+        <v>1.532018805474812</v>
       </c>
       <c r="D48">
-        <v>2.351210129626352</v>
+        <v>2.355648805474812</v>
       </c>
       <c r="E48">
-        <v>1.13434</v>
+        <v>1.15963</v>
       </c>
       <c r="F48">
-        <v>1.16334</v>
+        <v>1.18863</v>
       </c>
       <c r="G48">
         <v>0.365</v>
@@ -5211,28 +5211,28 @@
         <v>0.236</v>
       </c>
       <c r="M48">
-        <v>0.074570094</v>
+        <v>0.07619118300000001</v>
       </c>
       <c r="N48">
-        <v>0.161429906</v>
+        <v>0.159808817</v>
       </c>
       <c r="O48">
-        <v>0.03551457932</v>
+        <v>0.03515793974</v>
       </c>
       <c r="P48">
-        <v>0.12591532668</v>
+        <v>0.12465087726</v>
       </c>
       <c r="Q48">
-        <v>0.12791532668</v>
+        <v>0.12665087726</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.195734610259018</v>
+        <v>0.1981896445605613</v>
       </c>
       <c r="T48">
-        <v>1.954150597688179</v>
+        <v>1.986147924652366</v>
       </c>
       <c r="U48">
         <v>0.0641</v>
@@ -5249,7 +5249,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>3.164807596997262</v>
+        <v>3.097471265146257</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5257,22 +5257,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1285395716170975</v>
+        <v>0.1283833736943252</v>
       </c>
       <c r="C49">
-        <v>1.532018805474812</v>
+        <v>1.511184271917223</v>
       </c>
       <c r="D49">
-        <v>2.355648805474812</v>
+        <v>2.360104271917223</v>
       </c>
       <c r="E49">
-        <v>1.15963</v>
+        <v>1.18492</v>
       </c>
       <c r="F49">
-        <v>1.18863</v>
+        <v>1.21392</v>
       </c>
       <c r="G49">
         <v>0.365</v>
@@ -5293,28 +5293,28 @@
         <v>0.236</v>
       </c>
       <c r="M49">
-        <v>0.07619118300000001</v>
+        <v>0.07781227200000002</v>
       </c>
       <c r="N49">
-        <v>0.159808817</v>
+        <v>0.158187728</v>
       </c>
       <c r="O49">
-        <v>0.03515793974</v>
+        <v>0.03480130015999999</v>
       </c>
       <c r="P49">
-        <v>0.12465087726</v>
+        <v>0.12338642784</v>
       </c>
       <c r="Q49">
-        <v>0.12665087726</v>
+        <v>0.12538642784</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1981896445605613</v>
+        <v>0.2007391032583177</v>
       </c>
       <c r="T49">
-        <v>1.986147924652366</v>
+        <v>2.019375918038252</v>
       </c>
       <c r="U49">
         <v>0.0641</v>
@@ -5331,7 +5331,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>3.097471265146257</v>
+        <v>3.032940613789043</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5339,22 +5339,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1283833736943252</v>
+        <v>0.1312083357715529</v>
       </c>
       <c r="C50">
-        <v>1.511184271917223</v>
+        <v>1.407831574567604</v>
       </c>
       <c r="D50">
-        <v>2.360104271917223</v>
+        <v>2.282041574567604</v>
       </c>
       <c r="E50">
-        <v>1.18492</v>
+        <v>1.21021</v>
       </c>
       <c r="F50">
-        <v>1.21392</v>
+        <v>1.23921</v>
       </c>
       <c r="G50">
         <v>0.365</v>
@@ -5375,45 +5375,45 @@
         <v>0.236</v>
       </c>
       <c r="M50">
-        <v>0.077812272</v>
+        <v>0.089099199</v>
       </c>
       <c r="N50">
-        <v>0.158187728</v>
+        <v>0.146900801</v>
       </c>
       <c r="O50">
-        <v>0.03480130015999999</v>
+        <v>0.03231817621999999</v>
       </c>
       <c r="P50">
-        <v>0.12338642784</v>
+        <v>0.11458262478</v>
       </c>
       <c r="Q50">
-        <v>0.12538642784</v>
+        <v>0.11658262478</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.2007391032583177</v>
+        <v>0.2033885407285352</v>
       </c>
       <c r="T50">
-        <v>2.019375918038252</v>
+        <v>2.05390696998829</v>
       </c>
       <c r="U50">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V50">
         <v>0.22</v>
       </c>
       <c r="W50">
-        <v>0.04999800000000001</v>
+        <v>0.05608200000000001</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y50">
-        <v>3.032940613789043</v>
+        <v>2.648733127219247</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5421,22 +5421,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1312083357715529</v>
+        <v>0.1311129778487807</v>
       </c>
       <c r="C51">
-        <v>1.407831574567604</v>
+        <v>1.385092308930862</v>
       </c>
       <c r="D51">
-        <v>2.282041574567604</v>
+        <v>2.284592308930862</v>
       </c>
       <c r="E51">
-        <v>1.21021</v>
+        <v>1.2355</v>
       </c>
       <c r="F51">
-        <v>1.23921</v>
+        <v>1.2645</v>
       </c>
       <c r="G51">
         <v>0.365</v>
@@ -5457,28 +5457,28 @@
         <v>0.236</v>
       </c>
       <c r="M51">
-        <v>0.089099199</v>
+        <v>0.09091755</v>
       </c>
       <c r="N51">
-        <v>0.146900801</v>
+        <v>0.14508245</v>
       </c>
       <c r="O51">
-        <v>0.03231817621999999</v>
+        <v>0.03191813899999999</v>
       </c>
       <c r="P51">
-        <v>0.11458262478</v>
+        <v>0.113164311</v>
       </c>
       <c r="Q51">
-        <v>0.11658262478</v>
+        <v>0.115164311</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.2033885407285352</v>
+        <v>0.2061439556975613</v>
       </c>
       <c r="T51">
-        <v>2.05390696998829</v>
+        <v>2.08981926401633</v>
       </c>
       <c r="U51">
         <v>0.07190000000000001</v>
@@ -5495,7 +5495,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>2.648733127219247</v>
+        <v>2.595758464674862</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5503,22 +5503,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1311129778487807</v>
+        <v>0.1310176199260084</v>
       </c>
       <c r="C52">
-        <v>1.385092308930862</v>
+        <v>1.36235875180207</v>
       </c>
       <c r="D52">
-        <v>2.284592308930862</v>
+        <v>2.28714875180207</v>
       </c>
       <c r="E52">
-        <v>1.2355</v>
+        <v>1.26079</v>
       </c>
       <c r="F52">
-        <v>1.2645</v>
+        <v>1.28979</v>
       </c>
       <c r="G52">
         <v>0.365</v>
@@ -5539,28 +5539,28 @@
         <v>0.236</v>
       </c>
       <c r="M52">
-        <v>0.09091755</v>
+        <v>0.09273590100000001</v>
       </c>
       <c r="N52">
-        <v>0.14508245</v>
+        <v>0.143264099</v>
       </c>
       <c r="O52">
-        <v>0.03191813899999999</v>
+        <v>0.03151810177999999</v>
       </c>
       <c r="P52">
-        <v>0.113164311</v>
+        <v>0.11174599722</v>
       </c>
       <c r="Q52">
-        <v>0.115164311</v>
+        <v>0.11374599722</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.2061439556975613</v>
+        <v>0.2090118365836906</v>
       </c>
       <c r="T52">
-        <v>2.08981926401633</v>
+        <v>2.127197365963883</v>
       </c>
       <c r="U52">
         <v>0.07190000000000001</v>
@@ -5577,7 +5577,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>2.595758464674862</v>
+        <v>2.544861239877315</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5585,22 +5585,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1310176199260084</v>
+        <v>0.1325041020032361</v>
       </c>
       <c r="C53">
-        <v>1.36235875180207</v>
+        <v>1.297857162627423</v>
       </c>
       <c r="D53">
-        <v>2.28714875180207</v>
+        <v>2.247937162627423</v>
       </c>
       <c r="E53">
-        <v>1.26079</v>
+        <v>1.28608</v>
       </c>
       <c r="F53">
-        <v>1.28979</v>
+        <v>1.31508</v>
       </c>
       <c r="G53">
         <v>0.365</v>
@@ -5621,45 +5621,45 @@
         <v>0.236</v>
       </c>
       <c r="M53">
-        <v>0.09273590100000001</v>
+        <v>0.09968306400000002</v>
       </c>
       <c r="N53">
-        <v>0.143264099</v>
+        <v>0.136316936</v>
       </c>
       <c r="O53">
-        <v>0.03151810177999999</v>
+        <v>0.02998972591999999</v>
       </c>
       <c r="P53">
-        <v>0.11174599722</v>
+        <v>0.10632721008</v>
       </c>
       <c r="Q53">
-        <v>0.11374599722</v>
+        <v>0.10832721008</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.2090118365836906</v>
+        <v>0.2119992125067419</v>
       </c>
       <c r="T53">
-        <v>2.127197365963883</v>
+        <v>2.166132888825916</v>
       </c>
       <c r="U53">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V53">
         <v>0.22</v>
       </c>
       <c r="W53">
-        <v>0.05608200000000001</v>
+        <v>0.05912400000000001</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y53">
-        <v>2.544861239877315</v>
+        <v>2.367503470800215</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5667,22 +5667,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1325041020032361</v>
+        <v>0.1324391640804639</v>
       </c>
       <c r="C54">
-        <v>1.297857162627423</v>
+        <v>1.274252040031458</v>
       </c>
       <c r="D54">
-        <v>2.247937162627423</v>
+        <v>2.249622040031458</v>
       </c>
       <c r="E54">
-        <v>1.28608</v>
+        <v>1.31137</v>
       </c>
       <c r="F54">
-        <v>1.31508</v>
+        <v>1.34037</v>
       </c>
       <c r="G54">
         <v>0.365</v>
@@ -5703,28 +5703,28 @@
         <v>0.236</v>
       </c>
       <c r="M54">
-        <v>0.09968306400000002</v>
+        <v>0.101600046</v>
       </c>
       <c r="N54">
-        <v>0.136316936</v>
+        <v>0.134399954</v>
       </c>
       <c r="O54">
-        <v>0.02998972591999999</v>
+        <v>0.02956798988</v>
       </c>
       <c r="P54">
-        <v>0.10632721008</v>
+        <v>0.10483196412</v>
       </c>
       <c r="Q54">
-        <v>0.10832721008</v>
+        <v>0.10683196412</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.2119992125067419</v>
+        <v>0.2151137108094976</v>
       </c>
       <c r="T54">
-        <v>2.166132888825916</v>
+        <v>2.206725242448035</v>
       </c>
       <c r="U54">
         <v>0.07580000000000001</v>
@@ -5741,7 +5741,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>2.367503470800215</v>
+        <v>2.322833593992664</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5749,22 +5749,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1324391640804639</v>
+        <v>0.1323742261576916</v>
       </c>
       <c r="C55">
-        <v>1.274252040031458</v>
+        <v>1.250649445033915</v>
       </c>
       <c r="D55">
-        <v>2.249622040031458</v>
+        <v>2.251309445033915</v>
       </c>
       <c r="E55">
-        <v>1.31137</v>
+        <v>1.33666</v>
       </c>
       <c r="F55">
-        <v>1.34037</v>
+        <v>1.36566</v>
       </c>
       <c r="G55">
         <v>0.365</v>
@@ -5785,28 +5785,28 @@
         <v>0.236</v>
       </c>
       <c r="M55">
-        <v>0.101600046</v>
+        <v>0.103517028</v>
       </c>
       <c r="N55">
-        <v>0.134399954</v>
+        <v>0.132482972</v>
       </c>
       <c r="O55">
-        <v>0.02956798988</v>
+        <v>0.02914625383999999</v>
       </c>
       <c r="P55">
-        <v>0.10483196412</v>
+        <v>0.10333671816</v>
       </c>
       <c r="Q55">
-        <v>0.10683196412</v>
+        <v>0.10533671816</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.2151137108094976</v>
+        <v>0.2183636220819383</v>
       </c>
       <c r="T55">
-        <v>2.206725242448035</v>
+        <v>2.249082481010247</v>
       </c>
       <c r="U55">
         <v>0.07580000000000001</v>
@@ -5823,7 +5823,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>2.322833593992664</v>
+        <v>2.279818157066874</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5831,22 +5831,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1323742261576916</v>
+        <v>0.1323092882349193</v>
       </c>
       <c r="C56">
-        <v>1.250649445033915</v>
+        <v>1.227049383326796</v>
       </c>
       <c r="D56">
-        <v>2.251309445033915</v>
+        <v>2.252999383326796</v>
       </c>
       <c r="E56">
-        <v>1.33666</v>
+        <v>1.36195</v>
       </c>
       <c r="F56">
-        <v>1.36566</v>
+        <v>1.39095</v>
       </c>
       <c r="G56">
         <v>0.365</v>
@@ -5867,28 +5867,28 @@
         <v>0.236</v>
       </c>
       <c r="M56">
-        <v>0.103517028</v>
+        <v>0.10543401</v>
       </c>
       <c r="N56">
-        <v>0.132482972</v>
+        <v>0.13056599</v>
       </c>
       <c r="O56">
-        <v>0.02914625383999999</v>
+        <v>0.02872451779999999</v>
       </c>
       <c r="P56">
-        <v>0.10333671816</v>
+        <v>0.1018414722</v>
       </c>
       <c r="Q56">
-        <v>0.10533671816</v>
+        <v>0.1038414722</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.2183636220819383</v>
+        <v>0.2217579738553763</v>
       </c>
       <c r="T56">
-        <v>2.249082481010247</v>
+        <v>2.293322263508558</v>
       </c>
       <c r="U56">
         <v>0.07580000000000001</v>
@@ -5905,7 +5905,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>2.279818157066874</v>
+        <v>2.238366917847475</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5913,22 +5913,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1323092882349193</v>
+        <v>0.1322443503121471</v>
       </c>
       <c r="C57">
-        <v>1.227049383326796</v>
+        <v>1.203451860619206</v>
       </c>
       <c r="D57">
-        <v>2.252999383326796</v>
+        <v>2.254691860619206</v>
       </c>
       <c r="E57">
-        <v>1.36195</v>
+        <v>1.38724</v>
       </c>
       <c r="F57">
-        <v>1.39095</v>
+        <v>1.41624</v>
       </c>
       <c r="G57">
         <v>0.365</v>
@@ -5949,28 +5949,28 @@
         <v>0.236</v>
       </c>
       <c r="M57">
-        <v>0.10543401</v>
+        <v>0.107350992</v>
       </c>
       <c r="N57">
-        <v>0.13056599</v>
+        <v>0.128649008</v>
       </c>
       <c r="O57">
-        <v>0.02872451779999999</v>
+        <v>0.02830278175999999</v>
       </c>
       <c r="P57">
-        <v>0.1018414722</v>
+        <v>0.10034622624</v>
       </c>
       <c r="Q57">
-        <v>0.1038414722</v>
+        <v>0.10234622624</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.2217579738553763</v>
+        <v>0.2253066143457888</v>
       </c>
       <c r="T57">
-        <v>2.293322263508558</v>
+        <v>2.339572945211336</v>
       </c>
       <c r="U57">
         <v>0.07580000000000001</v>
@@ -5987,7 +5987,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>2.238366917847475</v>
+        <v>2.198396080028771</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -5995,22 +5995,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1322443503121471</v>
+        <v>0.1321794123893748</v>
       </c>
       <c r="C58">
-        <v>1.203451860619206</v>
+        <v>1.179856882637417</v>
       </c>
       <c r="D58">
-        <v>2.254691860619206</v>
+        <v>2.256386882637417</v>
       </c>
       <c r="E58">
-        <v>1.38724</v>
+        <v>1.41253</v>
       </c>
       <c r="F58">
-        <v>1.41624</v>
+        <v>1.44153</v>
       </c>
       <c r="G58">
         <v>0.365</v>
@@ -6031,28 +6031,28 @@
         <v>0.236</v>
       </c>
       <c r="M58">
-        <v>0.107350992</v>
+        <v>0.109267974</v>
       </c>
       <c r="N58">
-        <v>0.128649008</v>
+        <v>0.126732026</v>
       </c>
       <c r="O58">
-        <v>0.02830278175999999</v>
+        <v>0.02788104571999999</v>
       </c>
       <c r="P58">
-        <v>0.10034622624</v>
+        <v>0.09885098027999997</v>
       </c>
       <c r="Q58">
-        <v>0.10234622624</v>
+        <v>0.10085098028</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.2253066143457888</v>
+        <v>0.229020307882267</v>
       </c>
       <c r="T58">
-        <v>2.339572945211336</v>
+        <v>2.387974821411919</v>
       </c>
       <c r="U58">
         <v>0.07580000000000001</v>
@@ -6069,7 +6069,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>2.198396080028771</v>
+        <v>2.159827727747564</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6077,22 +6077,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1321794123893748</v>
+        <v>0.1321144744666025</v>
       </c>
       <c r="C59">
-        <v>1.179856882637417</v>
+        <v>1.156264455124934</v>
       </c>
       <c r="D59">
-        <v>2.256386882637417</v>
+        <v>2.258084455124935</v>
       </c>
       <c r="E59">
-        <v>1.41253</v>
+        <v>1.43782</v>
       </c>
       <c r="F59">
-        <v>1.44153</v>
+        <v>1.46682</v>
       </c>
       <c r="G59">
         <v>0.365</v>
@@ -6113,28 +6113,28 @@
         <v>0.236</v>
       </c>
       <c r="M59">
-        <v>0.109267974</v>
+        <v>0.111184956</v>
       </c>
       <c r="N59">
-        <v>0.126732026</v>
+        <v>0.124815044</v>
       </c>
       <c r="O59">
-        <v>0.02788104571999999</v>
+        <v>0.02745930967999999</v>
       </c>
       <c r="P59">
-        <v>0.09885098027999997</v>
+        <v>0.09735573431999997</v>
       </c>
       <c r="Q59">
-        <v>0.10085098028</v>
+        <v>0.09935573431999997</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.229020307882267</v>
+        <v>0.2329108439681013</v>
       </c>
       <c r="T59">
-        <v>2.387974821411919</v>
+        <v>2.438681548860148</v>
       </c>
       <c r="U59">
         <v>0.07580000000000001</v>
@@ -6151,7 +6151,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>2.159827727747564</v>
+        <v>2.122589318648468</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6159,22 +6159,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1321144744666025</v>
+        <v>0.1320495365438303</v>
       </c>
       <c r="C60">
-        <v>1.156264455124936</v>
+        <v>1.132674583842561</v>
       </c>
       <c r="D60">
-        <v>2.258084455124936</v>
+        <v>2.259784583842561</v>
       </c>
       <c r="E60">
-        <v>1.43782</v>
+        <v>1.46311</v>
       </c>
       <c r="F60">
-        <v>1.46682</v>
+        <v>1.49211</v>
       </c>
       <c r="G60">
         <v>0.365</v>
@@ -6195,28 +6195,28 @@
         <v>0.236</v>
       </c>
       <c r="M60">
-        <v>0.111184956</v>
+        <v>0.113101938</v>
       </c>
       <c r="N60">
-        <v>0.124815044</v>
+        <v>0.122898062</v>
       </c>
       <c r="O60">
-        <v>0.02745930968</v>
+        <v>0.02703757364</v>
       </c>
       <c r="P60">
-        <v>0.09735573432</v>
+        <v>0.09586048836</v>
       </c>
       <c r="Q60">
-        <v>0.09935573432</v>
+        <v>0.09786048836</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.2329108439681012</v>
+        <v>0.236991162302025</v>
       </c>
       <c r="T60">
-        <v>2.438681548860147</v>
+        <v>2.491861775208291</v>
       </c>
       <c r="U60">
         <v>0.07580000000000001</v>
@@ -6233,7 +6233,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>2.122589318648469</v>
+        <v>2.086613228501885</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1320495365438303</v>
+        <v>0.131984598621058</v>
       </c>
       <c r="C61">
-        <v>1.132674583842561</v>
+        <v>1.109087274568462</v>
       </c>
       <c r="D61">
-        <v>2.259784583842561</v>
+        <v>2.261487274568462</v>
       </c>
       <c r="E61">
-        <v>1.46311</v>
+        <v>1.4884</v>
       </c>
       <c r="F61">
-        <v>1.49211</v>
+        <v>1.5174</v>
       </c>
       <c r="G61">
         <v>0.365</v>
@@ -6277,28 +6277,28 @@
         <v>0.236</v>
       </c>
       <c r="M61">
-        <v>0.113101938</v>
+        <v>0.11501892</v>
       </c>
       <c r="N61">
-        <v>0.122898062</v>
+        <v>0.12098108</v>
       </c>
       <c r="O61">
-        <v>0.02703757364</v>
+        <v>0.0266158376</v>
       </c>
       <c r="P61">
-        <v>0.09586048836</v>
+        <v>0.09436524239999999</v>
       </c>
       <c r="Q61">
-        <v>0.09786048836</v>
+        <v>0.0963652424</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.236991162302025</v>
+        <v>0.241275496552645</v>
       </c>
       <c r="T61">
-        <v>2.491861775208291</v>
+        <v>2.547701012873841</v>
       </c>
       <c r="U61">
         <v>0.07580000000000001</v>
@@ -6315,7 +6315,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>2.086613228501885</v>
+        <v>2.051836341360187</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6323,22 +6323,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.131984598621058</v>
+        <v>0.1319196606982857</v>
       </c>
       <c r="C62">
-        <v>1.109087274568462</v>
+        <v>1.08550253309823</v>
       </c>
       <c r="D62">
-        <v>2.261487274568462</v>
+        <v>2.26319253309823</v>
       </c>
       <c r="E62">
-        <v>1.4884</v>
+        <v>1.51369</v>
       </c>
       <c r="F62">
-        <v>1.5174</v>
+        <v>1.54269</v>
       </c>
       <c r="G62">
         <v>0.365</v>
@@ -6359,28 +6359,28 @@
         <v>0.236</v>
       </c>
       <c r="M62">
-        <v>0.11501892</v>
+        <v>0.116935902</v>
       </c>
       <c r="N62">
-        <v>0.12098108</v>
+        <v>0.119064098</v>
       </c>
       <c r="O62">
-        <v>0.0266158376</v>
+        <v>0.02619410156</v>
       </c>
       <c r="P62">
-        <v>0.09436524239999999</v>
+        <v>0.09286999643999999</v>
       </c>
       <c r="Q62">
-        <v>0.0963652424</v>
+        <v>0.09486999643999999</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.241275496552645</v>
+        <v>0.2457795402520147</v>
       </c>
       <c r="T62">
-        <v>2.547701012873841</v>
+        <v>2.606403801188906</v>
       </c>
       <c r="U62">
         <v>0.07580000000000001</v>
@@ -6397,7 +6397,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>2.051836341360187</v>
+        <v>2.018199680026413</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6405,22 +6405,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1319196606982857</v>
+        <v>0.1387218427755134</v>
       </c>
       <c r="C63">
-        <v>1.08550253309823</v>
+        <v>0.894539455314487</v>
       </c>
       <c r="D63">
-        <v>2.26319253309823</v>
+        <v>2.097519455314487</v>
       </c>
       <c r="E63">
-        <v>1.51369</v>
+        <v>1.53898</v>
       </c>
       <c r="F63">
-        <v>1.54269</v>
+        <v>1.56798</v>
       </c>
       <c r="G63">
         <v>0.365</v>
@@ -6441,45 +6441,45 @@
         <v>0.236</v>
       </c>
       <c r="M63">
-        <v>0.116935902</v>
+        <v>0.1411182</v>
       </c>
       <c r="N63">
-        <v>0.119064098</v>
+        <v>0.09488179999999999</v>
       </c>
       <c r="O63">
-        <v>0.02619410156</v>
+        <v>0.020873996</v>
       </c>
       <c r="P63">
-        <v>0.09286999643999999</v>
+        <v>0.07400780399999998</v>
       </c>
       <c r="Q63">
-        <v>0.09486999643999999</v>
+        <v>0.07600780399999998</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.2457795402520147</v>
+        <v>0.2505206388829301</v>
       </c>
       <c r="T63">
-        <v>2.606403801188906</v>
+        <v>2.668196209941607</v>
       </c>
       <c r="U63">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V63">
         <v>0.22</v>
       </c>
       <c r="W63">
-        <v>0.05912400000000001</v>
+        <v>0.0702</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y63">
-        <v>2.018199680026413</v>
+        <v>1.672356931990346</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6487,22 +6487,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1387218427755134</v>
+        <v>0.1387676648527412</v>
       </c>
       <c r="C64">
-        <v>0.894539455314487</v>
+        <v>0.8682156259866187</v>
       </c>
       <c r="D64">
-        <v>2.097519455314487</v>
+        <v>2.096485625986619</v>
       </c>
       <c r="E64">
-        <v>1.53898</v>
+        <v>1.56427</v>
       </c>
       <c r="F64">
-        <v>1.56798</v>
+        <v>1.59327</v>
       </c>
       <c r="G64">
         <v>0.365</v>
@@ -6523,28 +6523,28 @@
         <v>0.236</v>
       </c>
       <c r="M64">
-        <v>0.1411182</v>
+        <v>0.1433943</v>
       </c>
       <c r="N64">
-        <v>0.09488179999999999</v>
+        <v>0.09260569999999999</v>
       </c>
       <c r="O64">
-        <v>0.020873996</v>
+        <v>0.020373254</v>
       </c>
       <c r="P64">
-        <v>0.07400780399999998</v>
+        <v>0.07223244599999999</v>
       </c>
       <c r="Q64">
-        <v>0.07600780399999998</v>
+        <v>0.07423244599999999</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.2505206388829301</v>
+        <v>0.2555180131155168</v>
       </c>
       <c r="T64">
-        <v>2.668196209941607</v>
+        <v>2.733328748897156</v>
       </c>
       <c r="U64">
         <v>0.09</v>
@@ -6561,7 +6561,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>1.672356931990346</v>
+        <v>1.645811583863515</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6569,22 +6569,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1387676648527412</v>
+        <v>0.1388134869299689</v>
       </c>
       <c r="C65">
-        <v>0.8682156259866187</v>
+        <v>0.8418928152681784</v>
       </c>
       <c r="D65">
-        <v>2.096485625986619</v>
+        <v>2.095452815268179</v>
       </c>
       <c r="E65">
-        <v>1.56427</v>
+        <v>1.58956</v>
       </c>
       <c r="F65">
-        <v>1.59327</v>
+        <v>1.61856</v>
       </c>
       <c r="G65">
         <v>0.365</v>
@@ -6605,28 +6605,28 @@
         <v>0.236</v>
       </c>
       <c r="M65">
-        <v>0.1433943</v>
+        <v>0.1456704</v>
       </c>
       <c r="N65">
-        <v>0.09260569999999999</v>
+        <v>0.09032959999999998</v>
       </c>
       <c r="O65">
-        <v>0.020373254</v>
+        <v>0.01987251199999999</v>
       </c>
       <c r="P65">
-        <v>0.07223244599999999</v>
+        <v>0.07045708799999999</v>
       </c>
       <c r="Q65">
-        <v>0.07423244599999999</v>
+        <v>0.07245708799999999</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.2555180131155168</v>
+        <v>0.2607930192499137</v>
       </c>
       <c r="T65">
-        <v>2.733328748897156</v>
+        <v>2.802079762239125</v>
       </c>
       <c r="U65">
         <v>0.09</v>
@@ -6643,7 +6643,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>1.645811583863515</v>
+        <v>1.620095777865647</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6651,22 +6651,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1388134869299689</v>
+        <v>0.1388593090071967</v>
       </c>
       <c r="C66">
-        <v>0.8418928152681784</v>
+        <v>0.8155710216544851</v>
       </c>
       <c r="D66">
-        <v>2.095452815268179</v>
+        <v>2.094421021654485</v>
       </c>
       <c r="E66">
-        <v>1.58956</v>
+        <v>1.61485</v>
       </c>
       <c r="F66">
-        <v>1.61856</v>
+        <v>1.64385</v>
       </c>
       <c r="G66">
         <v>0.365</v>
@@ -6687,28 +6687,28 @@
         <v>0.236</v>
       </c>
       <c r="M66">
-        <v>0.1456704</v>
+        <v>0.1479465</v>
       </c>
       <c r="N66">
-        <v>0.09032959999999998</v>
+        <v>0.08805349999999998</v>
       </c>
       <c r="O66">
-        <v>0.01987251199999999</v>
+        <v>0.01937177</v>
       </c>
       <c r="P66">
-        <v>0.07045708799999999</v>
+        <v>0.06868172999999998</v>
       </c>
       <c r="Q66">
-        <v>0.07245708799999999</v>
+        <v>0.07068172999999998</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2607930192499137</v>
+        <v>0.2663694543062762</v>
       </c>
       <c r="T66">
-        <v>2.802079762239125</v>
+        <v>2.87475940491492</v>
       </c>
       <c r="U66">
         <v>0.09</v>
@@ -6725,7 +6725,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>1.620095777865647</v>
+        <v>1.595171227436945</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6733,22 +6733,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1388593090071967</v>
+        <v>0.1389051310844244</v>
       </c>
       <c r="C67">
-        <v>0.8155710216544851</v>
+        <v>0.7892502436438238</v>
       </c>
       <c r="D67">
-        <v>2.094421021654485</v>
+        <v>2.093390243643824</v>
       </c>
       <c r="E67">
-        <v>1.61485</v>
+        <v>1.64014</v>
       </c>
       <c r="F67">
-        <v>1.64385</v>
+        <v>1.66914</v>
       </c>
       <c r="G67">
         <v>0.365</v>
@@ -6769,28 +6769,28 @@
         <v>0.236</v>
       </c>
       <c r="M67">
-        <v>0.1479465</v>
+        <v>0.1502226</v>
       </c>
       <c r="N67">
-        <v>0.08805349999999998</v>
+        <v>0.08577739999999998</v>
       </c>
       <c r="O67">
-        <v>0.01937177</v>
+        <v>0.01887102799999999</v>
       </c>
       <c r="P67">
-        <v>0.06868172999999998</v>
+        <v>0.06690637199999998</v>
       </c>
       <c r="Q67">
-        <v>0.07068172999999998</v>
+        <v>0.06890637199999998</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2663694543062762</v>
+        <v>0.2722739149541894</v>
       </c>
       <c r="T67">
-        <v>2.87475940491492</v>
+        <v>2.951714320689292</v>
       </c>
       <c r="U67">
         <v>0.09</v>
@@ -6807,7 +6807,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>1.595171227436945</v>
+        <v>1.571001966415173</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6815,22 +6815,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1389051310844244</v>
+        <v>0.1389509531616521</v>
       </c>
       <c r="C68">
-        <v>0.7892502436438238</v>
+        <v>0.7629304797374297</v>
       </c>
       <c r="D68">
-        <v>2.093390243643824</v>
+        <v>2.09236047973743</v>
       </c>
       <c r="E68">
-        <v>1.64014</v>
+        <v>1.66543</v>
       </c>
       <c r="F68">
-        <v>1.66914</v>
+        <v>1.69443</v>
       </c>
       <c r="G68">
         <v>0.365</v>
@@ -6851,28 +6851,28 @@
         <v>0.236</v>
       </c>
       <c r="M68">
-        <v>0.1502226</v>
+        <v>0.1524987</v>
       </c>
       <c r="N68">
-        <v>0.08577739999999998</v>
+        <v>0.08350129999999997</v>
       </c>
       <c r="O68">
-        <v>0.01887102799999999</v>
+        <v>0.01837028599999999</v>
       </c>
       <c r="P68">
-        <v>0.06690637199999998</v>
+        <v>0.06513101399999999</v>
       </c>
       <c r="Q68">
-        <v>0.06890637199999998</v>
+        <v>0.06713101399999999</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2722739149541894</v>
+        <v>0.2785362217019762</v>
       </c>
       <c r="T68">
-        <v>2.951714320689292</v>
+        <v>3.033333170753019</v>
       </c>
       <c r="U68">
         <v>0.09</v>
@@ -6889,7 +6889,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>1.571001966415173</v>
+        <v>1.547554175871663</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6897,22 +6897,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1389509531616521</v>
+        <v>0.1389967752388799</v>
       </c>
       <c r="C69">
-        <v>0.7629304797374297</v>
+        <v>0.7366117284394895</v>
       </c>
       <c r="D69">
-        <v>2.09236047973743</v>
+        <v>2.09133172843949</v>
       </c>
       <c r="E69">
-        <v>1.66543</v>
+        <v>1.69072</v>
       </c>
       <c r="F69">
-        <v>1.69443</v>
+        <v>1.71972</v>
       </c>
       <c r="G69">
         <v>0.365</v>
@@ -6933,28 +6933,28 @@
         <v>0.236</v>
       </c>
       <c r="M69">
-        <v>0.1524987</v>
+        <v>0.1547748</v>
       </c>
       <c r="N69">
-        <v>0.08350129999999997</v>
+        <v>0.08122519999999997</v>
       </c>
       <c r="O69">
-        <v>0.01837028599999999</v>
+        <v>0.01786954399999999</v>
       </c>
       <c r="P69">
-        <v>0.06513101399999999</v>
+        <v>0.06335565599999998</v>
       </c>
       <c r="Q69">
-        <v>0.06713101399999999</v>
+        <v>0.06535565599999998</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2785362217019762</v>
+        <v>0.2851899226214996</v>
       </c>
       <c r="T69">
-        <v>3.033333170753019</v>
+        <v>3.12005319894573</v>
       </c>
       <c r="U69">
         <v>0.09</v>
@@ -6971,7 +6971,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>1.547554175871663</v>
+        <v>1.524796026226491</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6979,22 +6979,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1389967752388799</v>
+        <v>0.1390425973161076</v>
       </c>
       <c r="C70">
-        <v>0.7366117284394895</v>
+        <v>0.7102939882571309</v>
       </c>
       <c r="D70">
-        <v>2.09133172843949</v>
+        <v>2.090303988257131</v>
       </c>
       <c r="E70">
-        <v>1.69072</v>
+        <v>1.71601</v>
       </c>
       <c r="F70">
-        <v>1.71972</v>
+        <v>1.74501</v>
       </c>
       <c r="G70">
         <v>0.365</v>
@@ -7015,28 +7015,28 @@
         <v>0.236</v>
       </c>
       <c r="M70">
-        <v>0.1547748</v>
+        <v>0.1570509</v>
       </c>
       <c r="N70">
-        <v>0.08122519999999997</v>
+        <v>0.07894909999999997</v>
       </c>
       <c r="O70">
-        <v>0.01786954399999999</v>
+        <v>0.01736880199999999</v>
       </c>
       <c r="P70">
-        <v>0.06335565599999998</v>
+        <v>0.06158029799999998</v>
       </c>
       <c r="Q70">
-        <v>0.06535565599999998</v>
+        <v>0.06358029799999998</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2851899226214996</v>
+        <v>0.292272894568089</v>
       </c>
       <c r="T70">
-        <v>3.12005319894573</v>
+        <v>3.212368067667002</v>
       </c>
       <c r="U70">
         <v>0.09</v>
@@ -7053,7 +7053,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>1.524796026226491</v>
+        <v>1.502697533092774</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7061,22 +7061,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1390425973161076</v>
+        <v>0.1734532875663751</v>
       </c>
       <c r="C71">
-        <v>0.7102939882571309</v>
+        <v>0.1215339481188016</v>
       </c>
       <c r="D71">
-        <v>2.090303988257131</v>
+        <v>1.526833948118802</v>
       </c>
       <c r="E71">
-        <v>1.71601</v>
+        <v>1.7413</v>
       </c>
       <c r="F71">
-        <v>1.74501</v>
+        <v>1.7703</v>
       </c>
       <c r="G71">
         <v>0.365</v>
@@ -7097,45 +7097,45 @@
         <v>0.236</v>
       </c>
       <c r="M71">
-        <v>0.1570509</v>
+        <v>0.25988004</v>
       </c>
       <c r="N71">
-        <v>0.07894909999999997</v>
+        <v>-0.02388004000000005</v>
       </c>
       <c r="O71">
-        <v>0.01736880199999999</v>
+        <v>-0.005253608800000011</v>
       </c>
       <c r="P71">
-        <v>0.06158029799999998</v>
+        <v>-0.01862643120000004</v>
       </c>
       <c r="Q71">
-        <v>0.06358029799999998</v>
+        <v>-0.01662643120000003</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.292272894568089</v>
+        <v>0.304077137544962</v>
       </c>
       <c r="T71">
-        <v>3.212368067667002</v>
+        <v>3.366216925036646</v>
       </c>
       <c r="U71">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V71">
-        <v>0.22</v>
+        <v>0.1997844851801623</v>
       </c>
       <c r="W71">
-        <v>0.0702</v>
+        <v>0.1174716375755522</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y71">
-        <v>1.502697533092774</v>
+        <v>0.9081112962734651</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7143,22 +7143,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1734532875663751</v>
+        <v>0.1744632875663751</v>
       </c>
       <c r="C72">
-        <v>0.1215339481188016</v>
+        <v>0.08425838240873507</v>
       </c>
       <c r="D72">
-        <v>1.526833948118802</v>
+        <v>1.514848382408735</v>
       </c>
       <c r="E72">
-        <v>1.7413</v>
+        <v>1.76659</v>
       </c>
       <c r="F72">
-        <v>1.7703</v>
+        <v>1.79559</v>
       </c>
       <c r="G72">
         <v>0.365</v>
@@ -7179,37 +7179,37 @@
         <v>0.236</v>
       </c>
       <c r="M72">
-        <v>0.25988004</v>
+        <v>0.263592612</v>
       </c>
       <c r="N72">
-        <v>-0.02388004000000005</v>
+        <v>-0.02759261200000002</v>
       </c>
       <c r="O72">
-        <v>-0.005253608800000011</v>
+        <v>-0.006070374640000003</v>
       </c>
       <c r="P72">
-        <v>-0.01862643120000004</v>
+        <v>-0.02152223736000001</v>
       </c>
       <c r="Q72">
-        <v>-0.01662643120000003</v>
+        <v>-0.01952223736000001</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.304077137544962</v>
+        <v>0.3129832457361676</v>
       </c>
       <c r="T72">
-        <v>3.366216925036646</v>
+        <v>3.482293370727565</v>
       </c>
       <c r="U72">
         <v>0.1468</v>
       </c>
       <c r="V72">
-        <v>0.1997844851801623</v>
+        <v>0.1969706191917094</v>
       </c>
       <c r="W72">
-        <v>0.1174716375755522</v>
+        <v>0.1178847131026571</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7217,7 +7217,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.9081112962734651</v>
+        <v>0.8953209963259516</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7225,22 +7225,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1744632875663751</v>
+        <v>0.1754732875663751</v>
       </c>
       <c r="C73">
-        <v>0.08425838240873529</v>
+        <v>0.04716952317606871</v>
       </c>
       <c r="D73">
-        <v>1.514848382408735</v>
+        <v>1.503049523176069</v>
       </c>
       <c r="E73">
-        <v>1.76659</v>
+        <v>1.79188</v>
       </c>
       <c r="F73">
-        <v>1.79559</v>
+        <v>1.82088</v>
       </c>
       <c r="G73">
         <v>0.365</v>
@@ -7261,37 +7261,37 @@
         <v>0.236</v>
       </c>
       <c r="M73">
-        <v>0.263592612</v>
+        <v>0.267305184</v>
       </c>
       <c r="N73">
-        <v>-0.02759261200000002</v>
+        <v>-0.03130518399999999</v>
       </c>
       <c r="O73">
-        <v>-0.006070374640000003</v>
+        <v>-0.006887140479999997</v>
       </c>
       <c r="P73">
-        <v>-0.02152223736000001</v>
+        <v>-0.02441804351999999</v>
       </c>
       <c r="Q73">
-        <v>-0.01952223736000001</v>
+        <v>-0.02241804351999999</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.3129832457361675</v>
+        <v>0.3225255045124592</v>
       </c>
       <c r="T73">
-        <v>3.482293370727564</v>
+        <v>3.606660991110691</v>
       </c>
       <c r="U73">
         <v>0.1468</v>
       </c>
       <c r="V73">
-        <v>0.1969706191917094</v>
+        <v>0.1942349161473801</v>
       </c>
       <c r="W73">
-        <v>0.1178847131026571</v>
+        <v>0.1182863143095646</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7299,7 +7299,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.8953209963259516</v>
+        <v>0.8828859824880912</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7307,22 +7307,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1754732875663751</v>
+        <v>0.1764832875663751</v>
       </c>
       <c r="C74">
-        <v>0.04716952317606871</v>
+        <v>0.01026304147685542</v>
       </c>
       <c r="D74">
-        <v>1.503049523176069</v>
+        <v>1.491433041476855</v>
       </c>
       <c r="E74">
-        <v>1.79188</v>
+        <v>1.81717</v>
       </c>
       <c r="F74">
-        <v>1.82088</v>
+        <v>1.84617</v>
       </c>
       <c r="G74">
         <v>0.365</v>
@@ -7343,37 +7343,37 @@
         <v>0.236</v>
       </c>
       <c r="M74">
-        <v>0.267305184</v>
+        <v>0.271017756</v>
       </c>
       <c r="N74">
-        <v>-0.03130518399999999</v>
+        <v>-0.03501775600000001</v>
       </c>
       <c r="O74">
-        <v>-0.006887140479999997</v>
+        <v>-0.007703906320000002</v>
       </c>
       <c r="P74">
-        <v>-0.02441804351999999</v>
+        <v>-0.02731384968000001</v>
       </c>
       <c r="Q74">
-        <v>-0.02241804351999999</v>
+        <v>-0.02531384968000001</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.3225255045124592</v>
+        <v>0.3327745972721799</v>
       </c>
       <c r="T74">
-        <v>3.606660991110691</v>
+        <v>3.740241027818494</v>
       </c>
       <c r="U74">
         <v>0.1468</v>
       </c>
       <c r="V74">
-        <v>0.1942349161473801</v>
+        <v>0.1915741638713885</v>
       </c>
       <c r="W74">
-        <v>0.1182863143095646</v>
+        <v>0.1186769127436802</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7381,7 +7381,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.8828859824880912</v>
+        <v>0.8707916539608571</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7389,22 +7389,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1764832875663751</v>
+        <v>0.1774932875663751</v>
       </c>
       <c r="C75">
-        <v>0.01026304147685542</v>
+        <v>-0.02646525883235706</v>
       </c>
       <c r="D75">
-        <v>1.491433041476855</v>
+        <v>1.479994741167643</v>
       </c>
       <c r="E75">
-        <v>1.81717</v>
+        <v>1.84246</v>
       </c>
       <c r="F75">
-        <v>1.84617</v>
+        <v>1.87146</v>
       </c>
       <c r="G75">
         <v>0.365</v>
@@ -7425,37 +7425,37 @@
         <v>0.236</v>
       </c>
       <c r="M75">
-        <v>0.271017756</v>
+        <v>0.274730328</v>
       </c>
       <c r="N75">
-        <v>-0.03501775600000001</v>
+        <v>-0.03873032800000004</v>
       </c>
       <c r="O75">
-        <v>-0.007703906320000002</v>
+        <v>-0.008520672160000008</v>
       </c>
       <c r="P75">
-        <v>-0.02731384968000001</v>
+        <v>-0.03020965584000003</v>
       </c>
       <c r="Q75">
-        <v>-0.02531384968000001</v>
+        <v>-0.02820965584000003</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.3327745972721799</v>
+        <v>0.3438120817826484</v>
       </c>
       <c r="T75">
-        <v>3.740241027818494</v>
+        <v>3.884096451965359</v>
       </c>
       <c r="U75">
         <v>0.1468</v>
       </c>
       <c r="V75">
-        <v>0.1915741638713885</v>
+        <v>0.1889853238190725</v>
       </c>
       <c r="W75">
-        <v>0.1186769127436802</v>
+        <v>0.1190569544633602</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7463,7 +7463,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.8707916539608571</v>
+        <v>0.8590241991776022</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7471,22 +7471,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1774932875663751</v>
+        <v>0.1785032875663751</v>
       </c>
       <c r="C76">
-        <v>-0.02646525883235706</v>
+        <v>-0.06301944614822652</v>
       </c>
       <c r="D76">
-        <v>1.479994741167643</v>
+        <v>1.468730553851773</v>
       </c>
       <c r="E76">
-        <v>1.84246</v>
+        <v>1.86775</v>
       </c>
       <c r="F76">
-        <v>1.87146</v>
+        <v>1.89675</v>
       </c>
       <c r="G76">
         <v>0.365</v>
@@ -7507,37 +7507,37 @@
         <v>0.236</v>
       </c>
       <c r="M76">
-        <v>0.274730328</v>
+        <v>0.2784429</v>
       </c>
       <c r="N76">
-        <v>-0.03873032800000004</v>
+        <v>-0.04244290000000001</v>
       </c>
       <c r="O76">
-        <v>-0.008520672160000008</v>
+        <v>-0.009337438000000002</v>
       </c>
       <c r="P76">
-        <v>-0.03020965584000003</v>
+        <v>-0.033105462</v>
       </c>
       <c r="Q76">
-        <v>-0.02820965584000003</v>
+        <v>-0.031105462</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.3438120817826484</v>
+        <v>0.3557325650539543</v>
       </c>
       <c r="T76">
-        <v>3.884096451965359</v>
+        <v>4.039460310043974</v>
       </c>
       <c r="U76">
         <v>0.1468</v>
       </c>
       <c r="V76">
-        <v>0.1889853238190725</v>
+        <v>0.1864655195014848</v>
       </c>
       <c r="W76">
-        <v>0.1190569544633602</v>
+        <v>0.119426861737182</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7545,7 +7545,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.8590241991776022</v>
+        <v>0.8475705431885675</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7553,22 +7553,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1785032875663751</v>
+        <v>0.1795132875663751</v>
       </c>
       <c r="C77">
-        <v>-0.06301944614822652</v>
+        <v>-0.09940346594527871</v>
       </c>
       <c r="D77">
-        <v>1.468730553851773</v>
+        <v>1.457636534054721</v>
       </c>
       <c r="E77">
-        <v>1.86775</v>
+        <v>1.89304</v>
       </c>
       <c r="F77">
-        <v>1.89675</v>
+        <v>1.92204</v>
       </c>
       <c r="G77">
         <v>0.365</v>
@@ -7589,37 +7589,37 @@
         <v>0.236</v>
       </c>
       <c r="M77">
-        <v>0.2784429</v>
+        <v>0.282155472</v>
       </c>
       <c r="N77">
-        <v>-0.04244290000000001</v>
+        <v>-0.04615547200000003</v>
       </c>
       <c r="O77">
-        <v>-0.009337438000000002</v>
+        <v>-0.01015420384000001</v>
       </c>
       <c r="P77">
-        <v>-0.033105462</v>
+        <v>-0.03600126816000002</v>
       </c>
       <c r="Q77">
-        <v>-0.031105462</v>
+        <v>-0.03400126816000002</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.3557325650539543</v>
+        <v>0.3686464219312025</v>
       </c>
       <c r="T77">
-        <v>4.039460310043974</v>
+        <v>4.207771156295807</v>
       </c>
       <c r="U77">
         <v>0.1468</v>
       </c>
       <c r="V77">
-        <v>0.1864655195014848</v>
+        <v>0.1840120258238337</v>
       </c>
       <c r="W77">
-        <v>0.119426861737182</v>
+        <v>0.1197870346090612</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7627,7 +7627,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.8475705431885675</v>
+        <v>0.8364182991992442</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7635,22 +7635,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1795132875663751</v>
+        <v>0.1805232875663751</v>
       </c>
       <c r="C78">
-        <v>-0.09940346594527871</v>
+        <v>-0.1356211453835492</v>
       </c>
       <c r="D78">
-        <v>1.457636534054721</v>
+        <v>1.446708854616451</v>
       </c>
       <c r="E78">
-        <v>1.89304</v>
+        <v>1.91833</v>
       </c>
       <c r="F78">
-        <v>1.92204</v>
+        <v>1.94733</v>
       </c>
       <c r="G78">
         <v>0.365</v>
@@ -7671,37 +7671,37 @@
         <v>0.236</v>
       </c>
       <c r="M78">
-        <v>0.282155472</v>
+        <v>0.285868044</v>
       </c>
       <c r="N78">
-        <v>-0.04615547200000003</v>
+        <v>-0.04986804400000006</v>
       </c>
       <c r="O78">
-        <v>-0.01015420384000001</v>
+        <v>-0.01097096968000001</v>
       </c>
       <c r="P78">
-        <v>-0.03600126816000002</v>
+        <v>-0.03889707432000004</v>
       </c>
       <c r="Q78">
-        <v>-0.03400126816000002</v>
+        <v>-0.03689707432000004</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.3686464219312025</v>
+        <v>0.3826832228847331</v>
       </c>
       <c r="T78">
-        <v>4.207771156295807</v>
+        <v>4.390717728308668</v>
       </c>
       <c r="U78">
         <v>0.1468</v>
       </c>
       <c r="V78">
-        <v>0.1840120258238337</v>
+        <v>0.181622259254693</v>
       </c>
       <c r="W78">
-        <v>0.1197870346090612</v>
+        <v>0.1201378523414111</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7709,7 +7709,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.8364182991992442</v>
+        <v>0.8255557238849682</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7717,22 +7717,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1805232875663751</v>
+        <v>0.1815332875663751</v>
       </c>
       <c r="C79">
-        <v>-0.1356211453835492</v>
+        <v>-0.171676197710511</v>
       </c>
       <c r="D79">
-        <v>1.446708854616451</v>
+        <v>1.435943802289489</v>
       </c>
       <c r="E79">
-        <v>1.91833</v>
+        <v>1.94362</v>
       </c>
       <c r="F79">
-        <v>1.94733</v>
+        <v>1.97262</v>
       </c>
       <c r="G79">
         <v>0.365</v>
@@ -7753,37 +7753,37 @@
         <v>0.236</v>
       </c>
       <c r="M79">
-        <v>0.285868044</v>
+        <v>0.289580616</v>
       </c>
       <c r="N79">
-        <v>-0.04986804400000006</v>
+        <v>-0.05358061600000003</v>
       </c>
       <c r="O79">
-        <v>-0.01097096968000001</v>
+        <v>-0.01178773552000001</v>
       </c>
       <c r="P79">
-        <v>-0.03889707432000004</v>
+        <v>-0.04179288048000002</v>
       </c>
       <c r="Q79">
-        <v>-0.03689707432000004</v>
+        <v>-0.03979288048000001</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.3826832228847331</v>
+        <v>0.3979960966522209</v>
       </c>
       <c r="T79">
-        <v>4.390717728308668</v>
+        <v>4.590295806868153</v>
       </c>
       <c r="U79">
         <v>0.1468</v>
       </c>
       <c r="V79">
-        <v>0.181622259254693</v>
+        <v>0.1792937687514277</v>
       </c>
       <c r="W79">
-        <v>0.1201378523414111</v>
+        <v>0.1204796747472904</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7791,7 +7791,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.8255557238849682</v>
+        <v>0.8149716761428534</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7799,22 +7799,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1815332875663751</v>
+        <v>0.1825432875663751</v>
       </c>
       <c r="C80">
-        <v>-0.171676197710511</v>
+        <v>-0.2075722264679261</v>
       </c>
       <c r="D80">
-        <v>1.435943802289489</v>
+        <v>1.425337773532074</v>
       </c>
       <c r="E80">
-        <v>1.94362</v>
+        <v>1.96891</v>
       </c>
       <c r="F80">
-        <v>1.97262</v>
+        <v>1.99791</v>
       </c>
       <c r="G80">
         <v>0.365</v>
@@ -7835,37 +7835,37 @@
         <v>0.236</v>
       </c>
       <c r="M80">
-        <v>0.289580616</v>
+        <v>0.293293188</v>
       </c>
       <c r="N80">
-        <v>-0.05358061600000003</v>
+        <v>-0.05729318800000005</v>
       </c>
       <c r="O80">
-        <v>-0.01178773552000001</v>
+        <v>-0.01260450136000001</v>
       </c>
       <c r="P80">
-        <v>-0.04179288048000002</v>
+        <v>-0.04468868664000004</v>
       </c>
       <c r="Q80">
-        <v>-0.03979288048000001</v>
+        <v>-0.04268868664000004</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.3979960966522209</v>
+        <v>0.4147673393499458</v>
       </c>
       <c r="T80">
-        <v>4.590295806868153</v>
+        <v>4.808881321480923</v>
       </c>
       <c r="U80">
         <v>0.1468</v>
       </c>
       <c r="V80">
-        <v>0.1792937687514277</v>
+        <v>0.1770242273748274</v>
       </c>
       <c r="W80">
-        <v>0.1204796747472904</v>
+        <v>0.1208128434213754</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7873,7 +7873,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.8149716761428534</v>
+        <v>0.804655578976488</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7881,22 +7881,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1825432875663751</v>
+        <v>0.2301411240558716</v>
       </c>
       <c r="C81">
-        <v>-0.2075722264679261</v>
+        <v>-0.6008918489102857</v>
       </c>
       <c r="D81">
-        <v>1.425337773532074</v>
+        <v>1.057308151089714</v>
       </c>
       <c r="E81">
-        <v>1.96891</v>
+        <v>1.9942</v>
       </c>
       <c r="F81">
-        <v>1.99791</v>
+        <v>2.0232</v>
       </c>
       <c r="G81">
         <v>0.365</v>
@@ -7917,45 +7917,45 @@
         <v>0.236</v>
       </c>
       <c r="M81">
-        <v>0.293293188</v>
+        <v>0.40625856</v>
       </c>
       <c r="N81">
-        <v>-0.05729318800000005</v>
+        <v>-0.1702585600000001</v>
       </c>
       <c r="O81">
-        <v>-0.01260450136000001</v>
+        <v>-0.03745688320000001</v>
       </c>
       <c r="P81">
-        <v>-0.04468868664000004</v>
+        <v>-0.1328016768</v>
       </c>
       <c r="Q81">
-        <v>-0.04268868664000004</v>
+        <v>-0.1308016768</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.4147673393499458</v>
+        <v>0.4501548887649254</v>
       </c>
       <c r="T81">
-        <v>4.808881321480923</v>
+        <v>5.270099720091748</v>
       </c>
       <c r="U81">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V81">
-        <v>0.1770242273748274</v>
+        <v>0.1278003840706765</v>
       </c>
       <c r="W81">
-        <v>0.1208128434213754</v>
+        <v>0.1751376828786082</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y81">
-        <v>0.804655578976488</v>
+        <v>0.5809108366848934</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7963,22 +7963,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2301411240558716</v>
+        <v>0.2316911240558716</v>
       </c>
       <c r="C82">
-        <v>-0.6008918489102857</v>
+        <v>-0.6349979106911399</v>
       </c>
       <c r="D82">
-        <v>1.057308151089714</v>
+        <v>1.04849208930886</v>
       </c>
       <c r="E82">
-        <v>1.9942</v>
+        <v>2.01949</v>
       </c>
       <c r="F82">
-        <v>2.0232</v>
+        <v>2.04849</v>
       </c>
       <c r="G82">
         <v>0.365</v>
@@ -7999,37 +7999,37 @@
         <v>0.236</v>
       </c>
       <c r="M82">
-        <v>0.40625856</v>
+        <v>0.4113367920000001</v>
       </c>
       <c r="N82">
-        <v>-0.1702585600000001</v>
+        <v>-0.1753367920000001</v>
       </c>
       <c r="O82">
-        <v>-0.03745688320000001</v>
+        <v>-0.03857409424000002</v>
       </c>
       <c r="P82">
-        <v>-0.1328016768</v>
+        <v>-0.1367626977600001</v>
       </c>
       <c r="Q82">
-        <v>-0.1308016768</v>
+        <v>-0.13476269776</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.4501548887649254</v>
+        <v>0.4714367250157109</v>
       </c>
       <c r="T82">
-        <v>5.270099720091748</v>
+        <v>5.547473389570261</v>
       </c>
       <c r="U82">
         <v>0.2008</v>
       </c>
       <c r="V82">
-        <v>0.1278003840706765</v>
+        <v>0.1262226015512855</v>
       </c>
       <c r="W82">
-        <v>0.1751376828786082</v>
+        <v>0.1754545016085019</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8037,7 +8037,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.5809108366848934</v>
+        <v>0.5737390979603885</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8045,22 +8045,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2316911240558716</v>
+        <v>0.2332411240558716</v>
       </c>
       <c r="C83">
-        <v>-0.6349979106911399</v>
+        <v>-0.6689581678004837</v>
       </c>
       <c r="D83">
-        <v>1.04849208930886</v>
+        <v>1.039821832199517</v>
       </c>
       <c r="E83">
-        <v>2.01949</v>
+        <v>2.04478</v>
       </c>
       <c r="F83">
-        <v>2.04849</v>
+        <v>2.07378</v>
       </c>
       <c r="G83">
         <v>0.365</v>
@@ -8081,37 +8081,37 @@
         <v>0.236</v>
       </c>
       <c r="M83">
-        <v>0.4113367920000001</v>
+        <v>0.416415024</v>
       </c>
       <c r="N83">
-        <v>-0.1753367920000001</v>
+        <v>-0.180415024</v>
       </c>
       <c r="O83">
-        <v>-0.03857409424000002</v>
+        <v>-0.03969130528000001</v>
       </c>
       <c r="P83">
-        <v>-0.1367626977600001</v>
+        <v>-0.14072371872</v>
       </c>
       <c r="Q83">
-        <v>-0.13476269776</v>
+        <v>-0.13872371872</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.4714367250157109</v>
+        <v>0.4950832097388061</v>
       </c>
       <c r="T83">
-        <v>5.547473389570261</v>
+        <v>5.855666355657498</v>
       </c>
       <c r="U83">
         <v>0.2008</v>
       </c>
       <c r="V83">
-        <v>0.1262226015512855</v>
+        <v>0.1246833015323674</v>
       </c>
       <c r="W83">
-        <v>0.1754545016085019</v>
+        <v>0.1757635930523006</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8119,7 +8119,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.5737390979603885</v>
+        <v>0.566742279692579</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8127,22 +8127,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2332411240558716</v>
+        <v>0.2347911240558716</v>
       </c>
       <c r="C84">
-        <v>-0.6689581678004837</v>
+        <v>-0.702776207664582</v>
       </c>
       <c r="D84">
-        <v>1.039821832199517</v>
+        <v>1.031293792335418</v>
       </c>
       <c r="E84">
-        <v>2.04478</v>
+        <v>2.07007</v>
       </c>
       <c r="F84">
-        <v>2.07378</v>
+        <v>2.09907</v>
       </c>
       <c r="G84">
         <v>0.365</v>
@@ -8163,37 +8163,37 @@
         <v>0.236</v>
       </c>
       <c r="M84">
-        <v>0.416415024</v>
+        <v>0.421493256</v>
       </c>
       <c r="N84">
-        <v>-0.180415024</v>
+        <v>-0.1854932560000001</v>
       </c>
       <c r="O84">
-        <v>-0.03969130528000001</v>
+        <v>-0.04080851632000001</v>
       </c>
       <c r="P84">
-        <v>-0.14072371872</v>
+        <v>-0.14468473968</v>
       </c>
       <c r="Q84">
-        <v>-0.13872371872</v>
+        <v>-0.14268473968</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.4950832097388061</v>
+        <v>0.5215116338410888</v>
       </c>
       <c r="T84">
-        <v>5.855666355657498</v>
+        <v>6.200117317754998</v>
       </c>
       <c r="U84">
         <v>0.2008</v>
       </c>
       <c r="V84">
-        <v>0.1246833015323674</v>
+        <v>0.1231810930801702</v>
       </c>
       <c r="W84">
-        <v>0.1757635930523006</v>
+        <v>0.1760652365095018</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8201,7 +8201,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.566742279692579</v>
+        <v>0.5599140594553189</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8209,22 +8209,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2347911240558716</v>
+        <v>0.2363411240558716</v>
       </c>
       <c r="C85">
-        <v>-0.702776207664582</v>
+        <v>-0.7364555009787705</v>
       </c>
       <c r="D85">
-        <v>1.031293792335418</v>
+        <v>1.02290449902123</v>
       </c>
       <c r="E85">
-        <v>2.07007</v>
+        <v>2.09536</v>
       </c>
       <c r="F85">
-        <v>2.09907</v>
+        <v>2.12436</v>
       </c>
       <c r="G85">
         <v>0.365</v>
@@ -8245,37 +8245,37 @@
         <v>0.236</v>
       </c>
       <c r="M85">
-        <v>0.421493256</v>
+        <v>0.4265714880000001</v>
       </c>
       <c r="N85">
-        <v>-0.1854932560000001</v>
+        <v>-0.1905714880000001</v>
       </c>
       <c r="O85">
-        <v>-0.04080851632000001</v>
+        <v>-0.04192572736000001</v>
       </c>
       <c r="P85">
-        <v>-0.14468473968</v>
+        <v>-0.1486457606400001</v>
       </c>
       <c r="Q85">
-        <v>-0.14268473968</v>
+        <v>-0.1466457606400001</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.5215116338410888</v>
+        <v>0.5512436109561568</v>
       </c>
       <c r="T85">
-        <v>6.200117317754998</v>
+        <v>6.587624650114686</v>
       </c>
       <c r="U85">
         <v>0.2008</v>
       </c>
       <c r="V85">
-        <v>0.1231810930801702</v>
+        <v>0.1217146514958824</v>
       </c>
       <c r="W85">
-        <v>0.1760652365095018</v>
+        <v>0.1763596979796268</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8283,7 +8283,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.5599140594553189</v>
+        <v>0.5532484158903747</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8291,22 +8291,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2363411240558716</v>
+        <v>0.2378911240558716</v>
       </c>
       <c r="C86">
-        <v>-0.7364555009787701</v>
+        <v>-0.7699994064170128</v>
       </c>
       <c r="D86">
-        <v>1.02290449902123</v>
+        <v>1.014650593582987</v>
       </c>
       <c r="E86">
-        <v>2.09536</v>
+        <v>2.12065</v>
       </c>
       <c r="F86">
-        <v>2.12436</v>
+        <v>2.14965</v>
       </c>
       <c r="G86">
         <v>0.365</v>
@@ -8327,37 +8327,37 @@
         <v>0.236</v>
       </c>
       <c r="M86">
-        <v>0.426571488</v>
+        <v>0.43164972</v>
       </c>
       <c r="N86">
-        <v>-0.190571488</v>
+        <v>-0.19564972</v>
       </c>
       <c r="O86">
-        <v>-0.04192572736</v>
+        <v>-0.04304293839999999</v>
       </c>
       <c r="P86">
-        <v>-0.14864576064</v>
+        <v>-0.1526067816</v>
       </c>
       <c r="Q86">
-        <v>-0.14664576064</v>
+        <v>-0.1506067816</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.5512436109561565</v>
+        <v>0.584939851686567</v>
       </c>
       <c r="T86">
-        <v>6.587624650114682</v>
+        <v>7.026799626788995</v>
       </c>
       <c r="U86">
         <v>0.2008</v>
       </c>
       <c r="V86">
-        <v>0.1217146514958825</v>
+        <v>0.1202827144194603</v>
       </c>
       <c r="W86">
-        <v>0.1763596979796268</v>
+        <v>0.1766472309445724</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8365,7 +8365,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.5532484158903748</v>
+        <v>0.5467396109975469</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8373,22 +8373,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2378911240558716</v>
+        <v>0.2394411240558716</v>
       </c>
       <c r="C87">
-        <v>-0.7699994064170128</v>
+        <v>-0.8034111751152768</v>
       </c>
       <c r="D87">
-        <v>1.014650593582987</v>
+        <v>1.006528824884723</v>
       </c>
       <c r="E87">
-        <v>2.12065</v>
+        <v>2.14594</v>
       </c>
       <c r="F87">
-        <v>2.14965</v>
+        <v>2.17494</v>
       </c>
       <c r="G87">
         <v>0.365</v>
@@ -8409,37 +8409,37 @@
         <v>0.236</v>
       </c>
       <c r="M87">
-        <v>0.43164972</v>
+        <v>0.436727952</v>
       </c>
       <c r="N87">
-        <v>-0.19564972</v>
+        <v>-0.200727952</v>
       </c>
       <c r="O87">
-        <v>-0.04304293839999999</v>
+        <v>-0.04416014944</v>
       </c>
       <c r="P87">
-        <v>-0.1526067816</v>
+        <v>-0.15656780256</v>
       </c>
       <c r="Q87">
-        <v>-0.1506067816</v>
+        <v>-0.15456780256</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.584939851686567</v>
+        <v>0.6234498410927504</v>
       </c>
       <c r="T87">
-        <v>7.026799626788995</v>
+        <v>7.528713885845352</v>
       </c>
       <c r="U87">
         <v>0.2008</v>
       </c>
       <c r="V87">
-        <v>0.1202827144194603</v>
+        <v>0.1188840782052805</v>
       </c>
       <c r="W87">
-        <v>0.1766472309445724</v>
+        <v>0.1769280770963797</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8447,7 +8447,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.5467396109975469</v>
+        <v>0.540382173660366</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8455,22 +8455,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2394411240558716</v>
+        <v>0.2409911240558716</v>
       </c>
       <c r="C88">
-        <v>-0.8034111751152768</v>
+        <v>-0.8366939549412939</v>
       </c>
       <c r="D88">
-        <v>1.006528824884723</v>
+        <v>0.9985360450587061</v>
       </c>
       <c r="E88">
-        <v>2.14594</v>
+        <v>2.17123</v>
       </c>
       <c r="F88">
-        <v>2.17494</v>
+        <v>2.20023</v>
       </c>
       <c r="G88">
         <v>0.365</v>
@@ -8491,37 +8491,37 @@
         <v>0.236</v>
       </c>
       <c r="M88">
-        <v>0.436727952</v>
+        <v>0.441806184</v>
       </c>
       <c r="N88">
-        <v>-0.200727952</v>
+        <v>-0.205806184</v>
       </c>
       <c r="O88">
-        <v>-0.04416014944</v>
+        <v>-0.04527736048</v>
       </c>
       <c r="P88">
-        <v>-0.15656780256</v>
+        <v>-0.16052882352</v>
       </c>
       <c r="Q88">
-        <v>-0.15456780256</v>
+        <v>-0.15852882352</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.6234498410927504</v>
+        <v>0.6678844442537312</v>
       </c>
       <c r="T88">
-        <v>7.528713885845352</v>
+        <v>8.107845723218071</v>
       </c>
       <c r="U88">
         <v>0.2008</v>
       </c>
       <c r="V88">
-        <v>0.1188840782052805</v>
+        <v>0.1175175945477486</v>
       </c>
       <c r="W88">
-        <v>0.1769280770963797</v>
+        <v>0.1772024670148121</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8529,7 +8529,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.540382173660366</v>
+        <v>0.534170884307948</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8537,22 +8537,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2409911240558716</v>
+        <v>0.2425411240558716</v>
       </c>
       <c r="C89">
-        <v>-0.8366939549412939</v>
+        <v>-0.8698507945624878</v>
       </c>
       <c r="D89">
-        <v>0.9985360450587061</v>
+        <v>0.9906692054375122</v>
       </c>
       <c r="E89">
-        <v>2.17123</v>
+        <v>2.19652</v>
       </c>
       <c r="F89">
-        <v>2.20023</v>
+        <v>2.22552</v>
       </c>
       <c r="G89">
         <v>0.365</v>
@@ -8573,37 +8573,37 @@
         <v>0.236</v>
       </c>
       <c r="M89">
-        <v>0.441806184</v>
+        <v>0.446884416</v>
       </c>
       <c r="N89">
-        <v>-0.205806184</v>
+        <v>-0.210884416</v>
       </c>
       <c r="O89">
-        <v>-0.04527736048</v>
+        <v>-0.04639457152</v>
       </c>
       <c r="P89">
-        <v>-0.16052882352</v>
+        <v>-0.16448984448</v>
       </c>
       <c r="Q89">
-        <v>-0.15852882352</v>
+        <v>-0.16248984448</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.6678844442537312</v>
+        <v>0.7197248146082088</v>
       </c>
       <c r="T89">
-        <v>8.107845723218071</v>
+        <v>8.783499533486244</v>
       </c>
       <c r="U89">
         <v>0.2008</v>
       </c>
       <c r="V89">
-        <v>0.1175175945477486</v>
+        <v>0.1161821673369787</v>
       </c>
       <c r="W89">
-        <v>0.1772024670148121</v>
+        <v>0.1774706207987347</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8611,7 +8611,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.534170884307948</v>
+        <v>0.5281007606226304</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8619,22 +8619,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2425411240558716</v>
+        <v>0.2440911240558716</v>
       </c>
       <c r="C90">
-        <v>-0.8698507945624878</v>
+        <v>-0.9028846473231162</v>
       </c>
       <c r="D90">
-        <v>0.9906692054375122</v>
+        <v>0.9829253526768836</v>
       </c>
       <c r="E90">
-        <v>2.19652</v>
+        <v>2.22181</v>
       </c>
       <c r="F90">
-        <v>2.22552</v>
+        <v>2.25081</v>
       </c>
       <c r="G90">
         <v>0.365</v>
@@ -8655,37 +8655,37 @@
         <v>0.236</v>
       </c>
       <c r="M90">
-        <v>0.446884416</v>
+        <v>0.451962648</v>
       </c>
       <c r="N90">
-        <v>-0.210884416</v>
+        <v>-0.215962648</v>
       </c>
       <c r="O90">
-        <v>-0.04639457152</v>
+        <v>-0.04751178256000001</v>
       </c>
       <c r="P90">
-        <v>-0.16448984448</v>
+        <v>-0.16845086544</v>
       </c>
       <c r="Q90">
-        <v>-0.16248984448</v>
+        <v>-0.16645086544</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.7197248146082088</v>
+        <v>0.7809907068453189</v>
       </c>
       <c r="T90">
-        <v>8.783499533486244</v>
+        <v>9.581999491075905</v>
       </c>
       <c r="U90">
         <v>0.2008</v>
       </c>
       <c r="V90">
-        <v>0.1161821673369787</v>
+        <v>0.1148767497264508</v>
       </c>
       <c r="W90">
-        <v>0.1774706207987347</v>
+        <v>0.1777327486549287</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8693,7 +8693,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.5281007606226304</v>
+        <v>0.5221670442111401</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8701,22 +8701,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2440911240558716</v>
+        <v>0.2456411240558716</v>
       </c>
       <c r="C91">
-        <v>-0.9028846473231162</v>
+        <v>-0.9357983749409773</v>
       </c>
       <c r="D91">
-        <v>0.9829253526768836</v>
+        <v>0.9753016250590227</v>
       </c>
       <c r="E91">
-        <v>2.22181</v>
+        <v>2.2471</v>
       </c>
       <c r="F91">
-        <v>2.25081</v>
+        <v>2.2761</v>
       </c>
       <c r="G91">
         <v>0.365</v>
@@ -8737,37 +8737,37 @@
         <v>0.236</v>
       </c>
       <c r="M91">
-        <v>0.451962648</v>
+        <v>0.45704088</v>
       </c>
       <c r="N91">
-        <v>-0.215962648</v>
+        <v>-0.2210408800000001</v>
       </c>
       <c r="O91">
-        <v>-0.04751178256000001</v>
+        <v>-0.04862899360000001</v>
       </c>
       <c r="P91">
-        <v>-0.16845086544</v>
+        <v>-0.1724118864</v>
       </c>
       <c r="Q91">
-        <v>-0.16645086544</v>
+        <v>-0.1704118864</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.7809907068453189</v>
+        <v>0.8545097775298508</v>
       </c>
       <c r="T91">
-        <v>9.581999491075905</v>
+        <v>10.5401994401835</v>
       </c>
       <c r="U91">
         <v>0.2008</v>
       </c>
       <c r="V91">
-        <v>0.1148767497264508</v>
+        <v>0.1136003413961569</v>
       </c>
       <c r="W91">
-        <v>0.1777327486549287</v>
+        <v>0.1779890514476517</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8775,7 +8775,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.5221670442111401</v>
+        <v>0.5163651881643496</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8783,22 +8783,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2456411240558716</v>
+        <v>0.2471911240558716</v>
       </c>
       <c r="C92">
-        <v>-0.9357983749409773</v>
+        <v>-0.9685947510334119</v>
       </c>
       <c r="D92">
-        <v>0.9753016250590227</v>
+        <v>0.9677952489665882</v>
       </c>
       <c r="E92">
-        <v>2.2471</v>
+        <v>2.27239</v>
       </c>
       <c r="F92">
-        <v>2.2761</v>
+        <v>2.30139</v>
       </c>
       <c r="G92">
         <v>0.365</v>
@@ -8819,37 +8819,37 @@
         <v>0.236</v>
       </c>
       <c r="M92">
-        <v>0.45704088</v>
+        <v>0.462119112</v>
       </c>
       <c r="N92">
-        <v>-0.2210408800000001</v>
+        <v>-0.226119112</v>
       </c>
       <c r="O92">
-        <v>-0.04862899360000001</v>
+        <v>-0.04974620464</v>
       </c>
       <c r="P92">
-        <v>-0.1724118864</v>
+        <v>-0.17637290736</v>
       </c>
       <c r="Q92">
-        <v>-0.1704118864</v>
+        <v>-0.17437290736</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.8545097775298508</v>
+        <v>0.9443664194776121</v>
       </c>
       <c r="T92">
-        <v>10.5401994401835</v>
+        <v>11.711332711315</v>
       </c>
       <c r="U92">
         <v>0.2008</v>
       </c>
       <c r="V92">
-        <v>0.1136003413961569</v>
+        <v>0.1123519859961992</v>
       </c>
       <c r="W92">
-        <v>0.1779890514476517</v>
+        <v>0.1782397212119632</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8857,7 +8857,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.5163651881643496</v>
+        <v>0.5106908454372689</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8865,22 +8865,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2471911240558716</v>
+        <v>0.2487411240558716</v>
       </c>
       <c r="C93">
-        <v>-0.9685947510334119</v>
+        <v>-1.001276464481719</v>
       </c>
       <c r="D93">
-        <v>0.9677952489665882</v>
+        <v>0.9604035355182815</v>
       </c>
       <c r="E93">
-        <v>2.27239</v>
+        <v>2.29768</v>
       </c>
       <c r="F93">
-        <v>2.30139</v>
+        <v>2.32668</v>
       </c>
       <c r="G93">
         <v>0.365</v>
@@ -8901,37 +8901,37 @@
         <v>0.236</v>
       </c>
       <c r="M93">
-        <v>0.462119112</v>
+        <v>0.467197344</v>
       </c>
       <c r="N93">
-        <v>-0.226119112</v>
+        <v>-0.231197344</v>
       </c>
       <c r="O93">
-        <v>-0.04974620464</v>
+        <v>-0.05086341568</v>
       </c>
       <c r="P93">
-        <v>-0.17637290736</v>
+        <v>-0.18033392832</v>
       </c>
       <c r="Q93">
-        <v>-0.17437290736</v>
+        <v>-0.17833392832</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.9443664194776121</v>
+        <v>1.056687221912314</v>
       </c>
       <c r="T93">
-        <v>11.711332711315</v>
+        <v>13.17524930022937</v>
       </c>
       <c r="U93">
         <v>0.2008</v>
       </c>
       <c r="V93">
-        <v>0.1123519859961992</v>
+        <v>0.1111307687571101</v>
       </c>
       <c r="W93">
-        <v>0.1782397212119632</v>
+        <v>0.1784849416335723</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8939,7 +8939,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.5106908454372689</v>
+        <v>0.5051398579868638</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8947,22 +8947,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2487411240558716</v>
+        <v>0.2842081569999103</v>
       </c>
       <c r="C94">
-        <v>-1.001276464481719</v>
+        <v>-1.169441877229492</v>
       </c>
       <c r="D94">
-        <v>0.9604035355182815</v>
+        <v>0.8175281227705086</v>
       </c>
       <c r="E94">
-        <v>2.29768</v>
+        <v>2.32297</v>
       </c>
       <c r="F94">
-        <v>2.32668</v>
+        <v>2.35197</v>
       </c>
       <c r="G94">
         <v>0.365</v>
@@ -8983,45 +8983,45 @@
         <v>0.236</v>
       </c>
       <c r="M94">
-        <v>0.467197344</v>
+        <v>0.554594526</v>
       </c>
       <c r="N94">
-        <v>-0.231197344</v>
+        <v>-0.318594526</v>
       </c>
       <c r="O94">
-        <v>-0.05086341568</v>
+        <v>-0.07009079572000002</v>
       </c>
       <c r="P94">
-        <v>-0.18033392832</v>
+        <v>-0.24850373028</v>
       </c>
       <c r="Q94">
-        <v>-0.17833392832</v>
+        <v>-0.24650373028</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>1.056687221912314</v>
+        <v>1.220628724243197</v>
       </c>
       <c r="T94">
-        <v>13.17524930022937</v>
+        <v>15.31195665693872</v>
       </c>
       <c r="U94">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.1111307687571101</v>
+        <v>0.09361794530225852</v>
       </c>
       <c r="W94">
-        <v>0.1784849416335723</v>
+        <v>0.2137248884977274</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y94">
-        <v>0.5051398579868638</v>
+        <v>0.425536115010266</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9029,22 +9029,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2842081569999103</v>
+        <v>0.2861081569999102</v>
       </c>
       <c r="C95">
-        <v>-1.169441877229492</v>
+        <v>-1.201195675431999</v>
       </c>
       <c r="D95">
-        <v>0.8175281227705086</v>
+        <v>0.8110643245680008</v>
       </c>
       <c r="E95">
-        <v>2.32297</v>
+        <v>2.34826</v>
       </c>
       <c r="F95">
-        <v>2.35197</v>
+        <v>2.37726</v>
       </c>
       <c r="G95">
         <v>0.365</v>
@@ -9065,37 +9065,37 @@
         <v>0.236</v>
       </c>
       <c r="M95">
-        <v>0.554594526</v>
+        <v>0.560557908</v>
       </c>
       <c r="N95">
-        <v>-0.318594526</v>
+        <v>-0.3245579080000001</v>
       </c>
       <c r="O95">
-        <v>-0.07009079572000002</v>
+        <v>-0.07140273976000001</v>
       </c>
       <c r="P95">
-        <v>-0.24850373028</v>
+        <v>-0.2531551682400001</v>
       </c>
       <c r="Q95">
-        <v>-0.24650373028</v>
+        <v>-0.2511551682400001</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>1.220628724243197</v>
+        <v>1.416433511617063</v>
       </c>
       <c r="T95">
-        <v>15.31195665693872</v>
+        <v>17.86394943309518</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.09361794530225852</v>
+        <v>0.09262200971393662</v>
       </c>
       <c r="W95">
-        <v>0.2137248884977274</v>
+        <v>0.2139597301094537</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9103,7 +9103,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.425536115010266</v>
+        <v>0.4210091350633482</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9111,22 +9111,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2861081569999102</v>
+        <v>0.2880081569999103</v>
       </c>
       <c r="C96">
-        <v>-1.201195675431999</v>
+        <v>-1.232848063205256</v>
       </c>
       <c r="D96">
-        <v>0.8110643245680008</v>
+        <v>0.8047019367947441</v>
       </c>
       <c r="E96">
-        <v>2.34826</v>
+        <v>2.37355</v>
       </c>
       <c r="F96">
-        <v>2.37726</v>
+        <v>2.40255</v>
       </c>
       <c r="G96">
         <v>0.365</v>
@@ -9147,37 +9147,37 @@
         <v>0.236</v>
       </c>
       <c r="M96">
-        <v>0.560557908</v>
+        <v>0.5665212900000001</v>
       </c>
       <c r="N96">
-        <v>-0.3245579080000001</v>
+        <v>-0.3305212900000001</v>
       </c>
       <c r="O96">
-        <v>-0.07140273976000001</v>
+        <v>-0.07271468380000001</v>
       </c>
       <c r="P96">
-        <v>-0.2531551682400001</v>
+        <v>-0.2578066062000001</v>
       </c>
       <c r="Q96">
-        <v>-0.2511551682400001</v>
+        <v>-0.2558066062000001</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.416433511617063</v>
+        <v>1.690560213940477</v>
       </c>
       <c r="T96">
-        <v>17.86394943309518</v>
+        <v>21.43673931971422</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.09262200971393662</v>
+        <v>0.09164704119063202</v>
       </c>
       <c r="W96">
-        <v>0.2139597301094537</v>
+        <v>0.214189627687249</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9185,7 +9185,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.4210091350633482</v>
+        <v>0.4165774599574184</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9193,22 +9193,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2880081569999103</v>
+        <v>0.2899081569999102</v>
       </c>
       <c r="C97">
-        <v>-1.232848063205256</v>
+        <v>-1.264401408513748</v>
       </c>
       <c r="D97">
-        <v>0.8047019367947441</v>
+        <v>0.7984385914862523</v>
       </c>
       <c r="E97">
-        <v>2.37355</v>
+        <v>2.39884</v>
       </c>
       <c r="F97">
-        <v>2.40255</v>
+        <v>2.42784</v>
       </c>
       <c r="G97">
         <v>0.365</v>
@@ -9229,37 +9229,37 @@
         <v>0.236</v>
       </c>
       <c r="M97">
-        <v>0.5665212900000001</v>
+        <v>0.5724846720000001</v>
       </c>
       <c r="N97">
-        <v>-0.3305212900000001</v>
+        <v>-0.3364846720000001</v>
       </c>
       <c r="O97">
-        <v>-0.07271468380000001</v>
+        <v>-0.07402662784000003</v>
       </c>
       <c r="P97">
-        <v>-0.2578066062000001</v>
+        <v>-0.2624580441600001</v>
       </c>
       <c r="Q97">
-        <v>-0.2558066062000001</v>
+        <v>-0.2604580441600001</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.690560213940477</v>
+        <v>2.101750267425596</v>
       </c>
       <c r="T97">
-        <v>21.43673931971422</v>
+        <v>26.79592414964279</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.09164704119063202</v>
+        <v>0.09069238451156295</v>
       </c>
       <c r="W97">
-        <v>0.214189627687249</v>
+        <v>0.2144147357321735</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9267,7 +9267,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.4165774599574184</v>
+        <v>0.4122381114161952</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9275,22 +9275,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2899081569999102</v>
+        <v>0.2918081569999103</v>
       </c>
       <c r="C98">
-        <v>-1.264401408513748</v>
+        <v>-1.295858006167761</v>
       </c>
       <c r="D98">
-        <v>0.7984385914862523</v>
+        <v>0.7922719938322388</v>
       </c>
       <c r="E98">
-        <v>2.39884</v>
+        <v>2.42413</v>
       </c>
       <c r="F98">
-        <v>2.42784</v>
+        <v>2.45313</v>
       </c>
       <c r="G98">
         <v>0.365</v>
@@ -9311,37 +9311,37 @@
         <v>0.236</v>
       </c>
       <c r="M98">
-        <v>0.572484672</v>
+        <v>0.578448054</v>
       </c>
       <c r="N98">
-        <v>-0.336484672</v>
+        <v>-0.342448054</v>
       </c>
       <c r="O98">
-        <v>-0.07402662784</v>
+        <v>-0.07533857188</v>
       </c>
       <c r="P98">
-        <v>-0.26245804416</v>
+        <v>-0.26710948212</v>
       </c>
       <c r="Q98">
-        <v>-0.26045804416</v>
+        <v>-0.26510948212</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>2.101750267425591</v>
+        <v>2.787067023234121</v>
       </c>
       <c r="T98">
-        <v>26.79592414964272</v>
+        <v>35.72789886619029</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.09069238451156296</v>
+        <v>0.08975741147536127</v>
       </c>
       <c r="W98">
-        <v>0.2144147357321735</v>
+        <v>0.2146352023741098</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9349,7 +9349,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.4122381114161953</v>
+        <v>0.4079882339789149</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9357,22 +9357,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2918081569999103</v>
+        <v>0.2937081569999102</v>
       </c>
       <c r="C99">
-        <v>-1.295858006167761</v>
+        <v>-1.327220080626698</v>
       </c>
       <c r="D99">
-        <v>0.7922719938322388</v>
+        <v>0.786199919373302</v>
       </c>
       <c r="E99">
-        <v>2.42413</v>
+        <v>2.44942</v>
       </c>
       <c r="F99">
-        <v>2.45313</v>
+        <v>2.47842</v>
       </c>
       <c r="G99">
         <v>0.365</v>
@@ -9393,37 +9393,37 @@
         <v>0.236</v>
       </c>
       <c r="M99">
-        <v>0.578448054</v>
+        <v>0.584411436</v>
       </c>
       <c r="N99">
-        <v>-0.342448054</v>
+        <v>-0.348411436</v>
       </c>
       <c r="O99">
-        <v>-0.07533857188</v>
+        <v>-0.07665051592000001</v>
       </c>
       <c r="P99">
-        <v>-0.26710948212</v>
+        <v>-0.27176092008</v>
       </c>
       <c r="Q99">
-        <v>-0.26510948212</v>
+        <v>-0.26976092008</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>2.787067023234121</v>
+        <v>4.157700534851181</v>
       </c>
       <c r="T99">
-        <v>35.72789886619029</v>
+        <v>53.59184829928544</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.08975741147536127</v>
+        <v>0.08884151952153105</v>
       </c>
       <c r="W99">
-        <v>0.2146352023741098</v>
+        <v>0.214851169696823</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9431,7 +9431,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.4079882339789149</v>
+        <v>0.4038250887342321</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9439,22 +9439,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2937081569999102</v>
+        <v>0.2956081569999102</v>
       </c>
       <c r="C100">
-        <v>-1.327220080626698</v>
+        <v>-1.358489788674461</v>
       </c>
       <c r="D100">
-        <v>0.786199919373302</v>
+        <v>0.7802202113255386</v>
       </c>
       <c r="E100">
-        <v>2.44942</v>
+        <v>2.47471</v>
       </c>
       <c r="F100">
-        <v>2.47842</v>
+        <v>2.50371</v>
       </c>
       <c r="G100">
         <v>0.365</v>
@@ -9475,37 +9475,37 @@
         <v>0.236</v>
       </c>
       <c r="M100">
-        <v>0.584411436</v>
+        <v>0.590374818</v>
       </c>
       <c r="N100">
-        <v>-0.348411436</v>
+        <v>-0.354374818</v>
       </c>
       <c r="O100">
-        <v>-0.07665051592000001</v>
+        <v>-0.07796245996000001</v>
       </c>
       <c r="P100">
-        <v>-0.27176092008</v>
+        <v>-0.27641235804</v>
       </c>
       <c r="Q100">
-        <v>-0.26976092008</v>
+        <v>-0.27441235804</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>4.157700534851181</v>
+        <v>8.269601069702363</v>
       </c>
       <c r="T100">
-        <v>53.59184829928544</v>
+        <v>107.1836965985709</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.08884151952153105</v>
+        <v>0.08794413043545497</v>
       </c>
       <c r="W100">
-        <v>0.214851169696823</v>
+        <v>0.2150627740433197</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9513,91 +9513,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.4038250887342321</v>
+        <v>0.3997460474338863</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2956081569999102</v>
-      </c>
-      <c r="C101">
-        <v>-1.358489788674461</v>
-      </c>
-      <c r="D101">
-        <v>0.7802202113255386</v>
-      </c>
-      <c r="E101">
-        <v>2.47471</v>
-      </c>
-      <c r="F101">
-        <v>2.50371</v>
-      </c>
-      <c r="G101">
-        <v>0.365</v>
-      </c>
-      <c r="H101">
-        <v>2.5</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>0.238</v>
-      </c>
-      <c r="K101">
-        <v>0.002000000000000002</v>
-      </c>
-      <c r="L101">
-        <v>0.236</v>
-      </c>
-      <c r="M101">
-        <v>0.590374818</v>
-      </c>
-      <c r="N101">
-        <v>-0.354374818</v>
-      </c>
-      <c r="O101">
-        <v>-0.07796245996000001</v>
-      </c>
-      <c r="P101">
-        <v>-0.27641235804</v>
-      </c>
-      <c r="Q101">
-        <v>-0.27441235804</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>8.269601069702363</v>
-      </c>
-      <c r="T101">
-        <v>107.1836965985709</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.08794413043545497</v>
-      </c>
-      <c r="W101">
-        <v>0.2150627740433197</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.3997460474338863</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
